--- a/research/traditional_assets/database/data/bahrain/bahrain_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_telecom_wireless.xlsx
@@ -1133,43 +1133,43 @@
         <v>1.43835616438356</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>66.4177938196167</v>
       </c>
       <c r="G2">
         <v>0.914893617021276</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0304255319148936</v>
       </c>
       <c r="I2">
         <v>0.300699300699301</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>110</v>
       </c>
       <c r="L2">
-        <v>188.449756920893</v>
+        <v>186.781418213102</v>
       </c>
       <c r="M2">
         <v>131.1</v>
       </c>
       <c r="N2">
-        <v>162.249756920893</v>
+        <v>162.154418213102</v>
       </c>
       <c r="O2">
         <v>47.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.573</v>
       </c>
       <c r="Q2">
         <v>0.138262630561607</v>
       </c>
       <c r="R2">
-        <v>0.120077182362397</v>
+        <v>0.120122182362397</v>
       </c>
       <c r="S2">
         <v>0.106277188197372</v>
@@ -1191,13 +1191,13 @@
         <v>0.152016370778228</v>
       </c>
       <c r="X2">
-        <v>0.120077182362397</v>
+        <v>0.120827456931715</v>
       </c>
       <c r="Y2">
         <v>0.909826460335579</v>
       </c>
       <c r="Z2">
-        <v>0.636242279954951</v>
+        <v>0.642668969651465</v>
       </c>
       <c r="AA2">
         <v>47.3</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1200771823623974</v>
+        <v>0.1201221823623974</v>
       </c>
       <c r="C2">
-        <v>188.4497569208933</v>
+        <v>186.7814182131021</v>
       </c>
       <c r="D2">
-        <v>162.2497569208933</v>
+        <v>162.1544182131021</v>
       </c>
       <c r="E2">
-        <v>-47.3</v>
+        <v>-45.727</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.573</v>
       </c>
       <c r="G2">
         <v>26.2</v>
@@ -1451,28 +1451,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07912190000000001</v>
       </c>
       <c r="N2">
-        <v>5.255102040816332</v>
+        <v>5.175980140816333</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>5.255102040816332</v>
+        <v>5.175980140816333</v>
       </c>
       <c r="Q2">
-        <v>52.75510204081633</v>
+        <v>52.67598014081634</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1200771823623974</v>
+        <v>0.1208274569317146</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6426689696514654</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>66.41779381961672</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1201221823623974</v>
+        <v>0.1201671823623974</v>
       </c>
       <c r="C3">
-        <v>186.7814182131021</v>
+        <v>185.1131914824441</v>
       </c>
       <c r="D3">
-        <v>162.1544182131021</v>
+        <v>162.0591914824441</v>
       </c>
       <c r="E3">
-        <v>-45.727</v>
+        <v>-44.154</v>
       </c>
       <c r="F3">
-        <v>1.573</v>
+        <v>3.146</v>
       </c>
       <c r="G3">
         <v>26.2</v>
@@ -1533,28 +1533,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M3">
-        <v>0.07912190000000001</v>
+        <v>0.1582438</v>
       </c>
       <c r="N3">
-        <v>5.175980140816333</v>
+        <v>5.096858240816332</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>5.175980140816333</v>
+        <v>5.096858240816332</v>
       </c>
       <c r="Q3">
-        <v>52.67598014081634</v>
+        <v>52.59685824081633</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1208274569317146</v>
+        <v>0.1215930432269361</v>
       </c>
       <c r="T3">
-        <v>0.6426689696514654</v>
+        <v>0.6492268162805619</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>66.41779381961672</v>
+        <v>33.20889690980836</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1201671823623974</v>
+        <v>0.1202121823623974</v>
       </c>
       <c r="C4">
-        <v>185.1131914824441</v>
+        <v>183.4450765317563</v>
       </c>
       <c r="D4">
-        <v>162.0591914824441</v>
+        <v>161.9640765317563</v>
       </c>
       <c r="E4">
-        <v>-44.154</v>
+        <v>-42.581</v>
       </c>
       <c r="F4">
-        <v>3.146</v>
+        <v>4.719</v>
       </c>
       <c r="G4">
         <v>26.2</v>
@@ -1615,28 +1615,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M4">
-        <v>0.1582438</v>
+        <v>0.2373657</v>
       </c>
       <c r="N4">
-        <v>5.096858240816332</v>
+        <v>5.017736340816333</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>5.096858240816332</v>
+        <v>5.017736340816333</v>
       </c>
       <c r="Q4">
-        <v>52.59685824081633</v>
+        <v>52.51773634081633</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1215930432269361</v>
+        <v>0.1223744148065952</v>
       </c>
       <c r="T4">
-        <v>0.6492268162805619</v>
+        <v>0.655919876242217</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.20889690980836</v>
+        <v>22.13926460653891</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1202121823623974</v>
+        <v>0.1202571823623974</v>
       </c>
       <c r="C5">
-        <v>183.4450765317563</v>
+        <v>181.7770731643379</v>
       </c>
       <c r="D5">
-        <v>161.9640765317563</v>
+        <v>161.8690731643379</v>
       </c>
       <c r="E5">
-        <v>-42.581</v>
+        <v>-41.008</v>
       </c>
       <c r="F5">
-        <v>4.719</v>
+        <v>6.292000000000001</v>
       </c>
       <c r="G5">
         <v>26.2</v>
@@ -1697,28 +1697,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M5">
-        <v>0.2373657</v>
+        <v>0.3164876</v>
       </c>
       <c r="N5">
-        <v>5.017736340816333</v>
+        <v>4.938614440816332</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>5.017736340816333</v>
+        <v>4.938614440816332</v>
       </c>
       <c r="Q5">
-        <v>52.51773634081633</v>
+        <v>52.43861444081633</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1223744148065952</v>
+        <v>0.1231720649608306</v>
       </c>
       <c r="T5">
-        <v>0.655919876242217</v>
+        <v>0.6627523749530736</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.13926460653891</v>
+        <v>16.60444845490418</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1202571823623974</v>
+        <v>0.1203021823623974</v>
       </c>
       <c r="C6">
-        <v>181.7770731643379</v>
+        <v>180.1091811839499</v>
       </c>
       <c r="D6">
-        <v>161.8690731643379</v>
+        <v>161.7741811839499</v>
       </c>
       <c r="E6">
-        <v>-41.008</v>
+        <v>-39.435</v>
       </c>
       <c r="F6">
-        <v>6.292000000000001</v>
+        <v>7.865000000000001</v>
       </c>
       <c r="G6">
         <v>26.2</v>
@@ -1779,28 +1779,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M6">
-        <v>0.3164876</v>
+        <v>0.3956095000000001</v>
       </c>
       <c r="N6">
-        <v>4.938614440816332</v>
+        <v>4.859492540816333</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>4.938614440816332</v>
+        <v>4.859492540816333</v>
       </c>
       <c r="Q6">
-        <v>52.43861444081633</v>
+        <v>52.35949254081633</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1231720649608306</v>
+        <v>0.123986507749892</v>
       </c>
       <c r="T6">
-        <v>0.6627523749530736</v>
+        <v>0.6697287157420533</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.60444845490418</v>
+        <v>13.28355876392334</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1203021823623974</v>
+        <v>0.1204371823623974</v>
       </c>
       <c r="C7">
-        <v>180.1091811839499</v>
+        <v>178.2521716094649</v>
       </c>
       <c r="D7">
-        <v>161.7741811839499</v>
+        <v>161.4901716094649</v>
       </c>
       <c r="E7">
-        <v>-39.435</v>
+        <v>-37.86199999999999</v>
       </c>
       <c r="F7">
-        <v>7.865000000000001</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="G7">
         <v>26.2</v>
@@ -1861,45 +1861,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M7">
-        <v>0.3956095000000001</v>
+        <v>0.4888884</v>
       </c>
       <c r="N7">
-        <v>4.859492540816333</v>
+        <v>4.766213640816332</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>4.859492540816333</v>
+        <v>4.766213640816332</v>
       </c>
       <c r="Q7">
-        <v>52.35949254081633</v>
+        <v>52.26621364081633</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.123986507749892</v>
+        <v>0.1248182791089334</v>
       </c>
       <c r="T7">
-        <v>0.6697287157420533</v>
+        <v>0.6768534893137773</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.28355876392334</v>
+        <v>10.74908310529833</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1204371823623974</v>
+        <v>0.1206161823623974</v>
       </c>
       <c r="C8">
-        <v>178.2521716094649</v>
+        <v>176.3041300813086</v>
       </c>
       <c r="D8">
-        <v>161.4901716094649</v>
+        <v>161.1151300813086</v>
       </c>
       <c r="E8">
-        <v>-37.86199999999999</v>
+        <v>-36.289</v>
       </c>
       <c r="F8">
-        <v>9.438000000000001</v>
+        <v>11.011</v>
       </c>
       <c r="G8">
         <v>26.2</v>
@@ -1943,45 +1943,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M8">
-        <v>0.4888884</v>
+        <v>0.5890884999999999</v>
       </c>
       <c r="N8">
-        <v>4.766213640816332</v>
+        <v>4.666013540816333</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>4.766213640816332</v>
+        <v>4.666013540816333</v>
       </c>
       <c r="Q8">
-        <v>52.26621364081633</v>
+        <v>52.16601354081633</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1248182791089334</v>
+        <v>0.1256679380240832</v>
       </c>
       <c r="T8">
-        <v>0.6768534893137773</v>
+        <v>0.6841314838225275</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.74908310529833</v>
+        <v>8.920734390191512</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1206161823623974</v>
+        <v>0.1206931823623974</v>
       </c>
       <c r="C9">
-        <v>176.3041300813086</v>
+        <v>174.5703346759176</v>
       </c>
       <c r="D9">
-        <v>161.1151300813086</v>
+        <v>160.9543346759176</v>
       </c>
       <c r="E9">
-        <v>-36.28899999999999</v>
+        <v>-34.71599999999999</v>
       </c>
       <c r="F9">
-        <v>11.011</v>
+        <v>12.584</v>
       </c>
       <c r="G9">
         <v>26.2</v>
@@ -2025,28 +2025,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M9">
-        <v>0.5890885</v>
+        <v>0.6732440000000001</v>
       </c>
       <c r="N9">
-        <v>4.666013540816333</v>
+        <v>4.581858040816332</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>4.666013540816333</v>
+        <v>4.581858040816332</v>
       </c>
       <c r="Q9">
-        <v>52.16601354081633</v>
+        <v>52.08185804081633</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1256679380240832</v>
+        <v>0.1265360677852146</v>
       </c>
       <c r="T9">
-        <v>0.6841314838225275</v>
+        <v>0.6915676956032072</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.920734390191512</v>
+        <v>7.805642591417572</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1206931823623974</v>
+        <v>0.1208421823623974</v>
       </c>
       <c r="C10">
-        <v>174.5703346759176</v>
+        <v>172.6870948002885</v>
       </c>
       <c r="D10">
-        <v>160.9543346759176</v>
+        <v>160.6440948002886</v>
       </c>
       <c r="E10">
-        <v>-34.71599999999999</v>
+        <v>-33.143</v>
       </c>
       <c r="F10">
-        <v>12.584</v>
+        <v>14.157</v>
       </c>
       <c r="G10">
         <v>26.2</v>
@@ -2107,45 +2107,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M10">
-        <v>0.6732440000000001</v>
+        <v>0.7687251000000001</v>
       </c>
       <c r="N10">
-        <v>4.581858040816332</v>
+        <v>4.486376940816332</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>4.581858040816332</v>
+        <v>4.486376940816332</v>
       </c>
       <c r="Q10">
-        <v>52.08185804081633</v>
+        <v>51.98637694081633</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1265360677852146</v>
+        <v>0.1274232773213158</v>
       </c>
       <c r="T10">
-        <v>0.6915676956032072</v>
+        <v>0.6991673406098359</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>7.805642591417572</v>
+        <v>6.836126517550073</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1208421823623974</v>
+        <v>0.1209271823623974</v>
       </c>
       <c r="C11">
-        <v>172.6870948002885</v>
+        <v>170.9376474733607</v>
       </c>
       <c r="D11">
-        <v>160.6440948002886</v>
+        <v>160.4676474733607</v>
       </c>
       <c r="E11">
-        <v>-33.143</v>
+        <v>-31.57</v>
       </c>
       <c r="F11">
-        <v>14.157</v>
+        <v>15.73</v>
       </c>
       <c r="G11">
         <v>26.2</v>
@@ -2189,28 +2189,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M11">
-        <v>0.7687251000000001</v>
+        <v>0.8541390000000001</v>
       </c>
       <c r="N11">
-        <v>4.486376940816332</v>
+        <v>4.400963040816332</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>4.486376940816332</v>
+        <v>4.400963040816332</v>
       </c>
       <c r="Q11">
-        <v>51.98637694081633</v>
+        <v>51.90096304081634</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1274232773213158</v>
+        <v>0.128330202624886</v>
       </c>
       <c r="T11">
-        <v>0.6991673406098359</v>
+        <v>0.7069358666166119</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>6.836126517550073</v>
+        <v>6.152513865795066</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1209271823623974</v>
+        <v>0.1211221823623974</v>
       </c>
       <c r="C12">
-        <v>170.9376474733607</v>
+        <v>168.9613174695675</v>
       </c>
       <c r="D12">
-        <v>160.4676474733607</v>
+        <v>160.0643174695675</v>
       </c>
       <c r="E12">
-        <v>-31.56999999999999</v>
+        <v>-29.997</v>
       </c>
       <c r="F12">
-        <v>15.73</v>
+        <v>17.303</v>
       </c>
       <c r="G12">
         <v>26.2</v>
@@ -2271,45 +2271,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M12">
-        <v>0.8541390000000001</v>
+        <v>0.9568559000000001</v>
       </c>
       <c r="N12">
-        <v>4.400963040816332</v>
+        <v>4.298246140816333</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>4.400963040816332</v>
+        <v>4.298246140816333</v>
       </c>
       <c r="Q12">
-        <v>51.90096304081634</v>
+        <v>51.79824614081633</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.128330202624886</v>
+        <v>0.1292575082723566</v>
       </c>
       <c r="T12">
-        <v>0.7069358666166119</v>
+        <v>0.7148789662415176</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.152513865795066</v>
+        <v>5.492051667148974</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1211221823623974</v>
+        <v>0.1212171823623974</v>
       </c>
       <c r="C13">
-        <v>168.9613174695675</v>
+        <v>167.1925569569811</v>
       </c>
       <c r="D13">
-        <v>160.0643174695675</v>
+        <v>159.8685569569811</v>
       </c>
       <c r="E13">
-        <v>-29.997</v>
+        <v>-28.424</v>
       </c>
       <c r="F13">
-        <v>17.303</v>
+        <v>18.876</v>
       </c>
       <c r="G13">
         <v>26.2</v>
@@ -2353,28 +2353,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M13">
-        <v>0.9568559000000001</v>
+        <v>1.0438428</v>
       </c>
       <c r="N13">
-        <v>4.298246140816333</v>
+        <v>4.211259240816332</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>4.298246140816333</v>
+        <v>4.211259240816332</v>
       </c>
       <c r="Q13">
-        <v>51.79824614081633</v>
+        <v>51.71125924081633</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1292575082723566</v>
+        <v>0.1302058890481789</v>
       </c>
       <c r="T13">
-        <v>0.7148789662415176</v>
+        <v>0.7230025908578984</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.492051667148974</v>
+        <v>5.034380694886559</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1212171823623974</v>
+        <v>0.1213121823623974</v>
       </c>
       <c r="C14">
-        <v>167.1925569569811</v>
+        <v>165.4242746942343</v>
       </c>
       <c r="D14">
-        <v>159.8685569569811</v>
+        <v>159.6732746942343</v>
       </c>
       <c r="E14">
-        <v>-28.424</v>
+        <v>-26.851</v>
       </c>
       <c r="F14">
-        <v>18.876</v>
+        <v>20.449</v>
       </c>
       <c r="G14">
         <v>26.2</v>
@@ -2435,28 +2435,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M14">
-        <v>1.0438428</v>
+        <v>1.1308297</v>
       </c>
       <c r="N14">
-        <v>4.211259240816332</v>
+        <v>4.124272340816333</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>4.211259240816332</v>
+        <v>4.124272340816333</v>
       </c>
       <c r="Q14">
-        <v>51.71125924081633</v>
+        <v>51.62427234081633</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1302058890481789</v>
+        <v>0.1311760716809166</v>
       </c>
       <c r="T14">
-        <v>0.7230025908578984</v>
+        <v>0.7313129654654604</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.034380694886559</v>
+        <v>4.647120641433748</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1213121823623974</v>
+        <v>0.1217571823623974</v>
       </c>
       <c r="C15">
-        <v>165.4242746942343</v>
+        <v>162.9428467232352</v>
       </c>
       <c r="D15">
-        <v>159.6732746942343</v>
+        <v>158.7648467232352</v>
       </c>
       <c r="E15">
-        <v>-26.851</v>
+        <v>-25.278</v>
       </c>
       <c r="F15">
-        <v>20.449</v>
+        <v>22.022</v>
       </c>
       <c r="G15">
         <v>26.2</v>
@@ -2517,45 +2517,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M15">
-        <v>1.1308297</v>
+        <v>1.2728716</v>
       </c>
       <c r="N15">
-        <v>4.124272340816333</v>
+        <v>3.982230440816332</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>4.124272340816333</v>
+        <v>3.982230440816332</v>
       </c>
       <c r="Q15">
-        <v>51.62427234081633</v>
+        <v>51.48223044081633</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1311760716809166</v>
+        <v>0.1321688167004621</v>
       </c>
       <c r="T15">
-        <v>0.7313129654654604</v>
+        <v>0.7398166045987798</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.647120641433748</v>
+        <v>4.128540569855067</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1217571823623974</v>
+        <v>0.1224021823623974</v>
       </c>
       <c r="C16">
-        <v>162.9428467232352</v>
+        <v>160.0713355516791</v>
       </c>
       <c r="D16">
-        <v>158.7648467232352</v>
+        <v>157.4663355516792</v>
       </c>
       <c r="E16">
-        <v>-25.278</v>
+        <v>-23.70499999999999</v>
       </c>
       <c r="F16">
-        <v>22.022</v>
+        <v>23.59500000000001</v>
       </c>
       <c r="G16">
         <v>26.2</v>
@@ -2599,45 +2599,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M16">
-        <v>1.2728716</v>
+        <v>1.4463735</v>
       </c>
       <c r="N16">
-        <v>3.982230440816332</v>
+        <v>3.808728540816332</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>3.982230440816332</v>
+        <v>3.808728540816332</v>
       </c>
       <c r="Q16">
-        <v>51.48223044081633</v>
+        <v>51.30872854081633</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1321688167004621</v>
+        <v>0.1331849204263499</v>
       </c>
       <c r="T16">
-        <v>0.7398166045987798</v>
+        <v>0.7485203293587654</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.128540569855067</v>
+        <v>3.63329530084472</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1224021823623974</v>
+        <v>0.1230051823623974</v>
       </c>
       <c r="C17">
-        <v>160.0713355516791</v>
+        <v>157.303443797641</v>
       </c>
       <c r="D17">
-        <v>157.4663355516792</v>
+        <v>156.271443797641</v>
       </c>
       <c r="E17">
-        <v>-23.70499999999999</v>
+        <v>-22.13199999999999</v>
       </c>
       <c r="F17">
-        <v>23.595</v>
+        <v>25.168</v>
       </c>
       <c r="G17">
         <v>26.2</v>
@@ -2681,45 +2681,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M17">
-        <v>1.4463735</v>
+        <v>1.6132688</v>
       </c>
       <c r="N17">
-        <v>3.808728540816332</v>
+        <v>3.641833240816332</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>3.808728540816332</v>
+        <v>3.641833240816332</v>
       </c>
       <c r="Q17">
-        <v>51.30872854081633</v>
+        <v>51.14183324081633</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1331849204263499</v>
+        <v>0.1342252170980922</v>
       </c>
       <c r="T17">
-        <v>0.7485203293587654</v>
+        <v>0.7574312856606555</v>
       </c>
       <c r="U17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.633295300844721</v>
+        <v>3.257424950396568</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1230051823623974</v>
+        <v>0.1231881823623974</v>
       </c>
       <c r="C18">
-        <v>157.303443797641</v>
+        <v>155.3713935261707</v>
       </c>
       <c r="D18">
-        <v>156.271443797641</v>
+        <v>155.9123935261707</v>
       </c>
       <c r="E18">
-        <v>-22.13199999999999</v>
+        <v>-20.55899999999999</v>
       </c>
       <c r="F18">
-        <v>25.168</v>
+        <v>26.741</v>
       </c>
       <c r="G18">
         <v>26.2</v>
@@ -2763,28 +2763,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M18">
-        <v>1.6132688</v>
+        <v>1.7140981</v>
       </c>
       <c r="N18">
-        <v>3.641833240816332</v>
+        <v>3.541003940816332</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>3.641833240816332</v>
+        <v>3.541003940816332</v>
       </c>
       <c r="Q18">
-        <v>51.14183324081633</v>
+        <v>51.04100394081633</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1342252170980922</v>
+        <v>0.1352905811595149</v>
       </c>
       <c r="T18">
-        <v>0.7574312856606555</v>
+        <v>0.7665569638011455</v>
       </c>
       <c r="U18">
         <v>0.0641</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.257424950396568</v>
+        <v>3.0658117180203</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1231881823623974</v>
+        <v>0.1247751823623974</v>
       </c>
       <c r="C19">
-        <v>155.3713935261707</v>
+        <v>150.7525063527982</v>
       </c>
       <c r="D19">
-        <v>155.9123935261707</v>
+        <v>152.8665063527982</v>
       </c>
       <c r="E19">
-        <v>-20.55899999999999</v>
+        <v>-18.98599999999999</v>
       </c>
       <c r="F19">
-        <v>26.741</v>
+        <v>28.314</v>
       </c>
       <c r="G19">
         <v>26.2</v>
@@ -2845,45 +2845,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M19">
-        <v>1.7140981</v>
+        <v>2.035776600000001</v>
       </c>
       <c r="N19">
-        <v>3.541003940816332</v>
+        <v>3.219325440816332</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>3.541003940816332</v>
+        <v>3.219325440816332</v>
       </c>
       <c r="Q19">
-        <v>51.04100394081633</v>
+        <v>50.71932544081633</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1352905811595149</v>
+        <v>0.1363819297102407</v>
       </c>
       <c r="T19">
-        <v>0.7665569638011455</v>
+        <v>0.7759052194572569</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.0658117180203</v>
+        <v>2.581374616849575</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1247751823623974</v>
+        <v>0.1257771823623974</v>
       </c>
       <c r="C20">
-        <v>150.7525063527981</v>
+        <v>147.3169379074466</v>
       </c>
       <c r="D20">
-        <v>152.8665063527981</v>
+        <v>151.0039379074466</v>
       </c>
       <c r="E20">
-        <v>-18.986</v>
+        <v>-17.41299999999999</v>
       </c>
       <c r="F20">
-        <v>28.314</v>
+        <v>29.887</v>
       </c>
       <c r="G20">
         <v>26.2</v>
@@ -2927,45 +2927,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M20">
-        <v>2.0357766</v>
+        <v>2.2654346</v>
       </c>
       <c r="N20">
-        <v>3.219325440816332</v>
+        <v>2.989667440816332</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>3.219325440816332</v>
+        <v>2.989667440816332</v>
       </c>
       <c r="Q20">
-        <v>50.71932544081633</v>
+        <v>50.48966744081633</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1363819297102407</v>
+        <v>0.1375002251387622</v>
       </c>
       <c r="T20">
-        <v>0.7759052194572569</v>
+        <v>0.7854842962406797</v>
       </c>
       <c r="U20">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.581374616849576</v>
+        <v>2.319688257968838</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1257771823623974</v>
+        <v>0.1260771823623974</v>
       </c>
       <c r="C21">
-        <v>147.3169379074466</v>
+        <v>145.1950795410283</v>
       </c>
       <c r="D21">
-        <v>151.0039379074466</v>
+        <v>150.4550795410283</v>
       </c>
       <c r="E21">
-        <v>-17.41299999999999</v>
+        <v>-15.83999999999999</v>
       </c>
       <c r="F21">
-        <v>29.887</v>
+        <v>31.46</v>
       </c>
       <c r="G21">
         <v>26.2</v>
@@ -3009,28 +3009,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M21">
-        <v>2.2654346</v>
+        <v>2.384668</v>
       </c>
       <c r="N21">
-        <v>2.989667440816332</v>
+        <v>2.870434040816332</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>2.989667440816332</v>
+        <v>2.870434040816332</v>
       </c>
       <c r="Q21">
-        <v>50.48966744081633</v>
+        <v>50.37043404081633</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1375002251387622</v>
+        <v>0.1386464779529968</v>
       </c>
       <c r="T21">
-        <v>0.7854842962406797</v>
+        <v>0.7953028499436883</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.319688257968838</v>
+        <v>2.203703845070396</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1260771823623974</v>
+        <v>0.1263771823623974</v>
       </c>
       <c r="C22">
-        <v>145.1950795410283</v>
+        <v>143.0771966275714</v>
       </c>
       <c r="D22">
-        <v>150.4550795410283</v>
+        <v>149.9101966275715</v>
       </c>
       <c r="E22">
-        <v>-15.83999999999999</v>
+        <v>-14.26699999999999</v>
       </c>
       <c r="F22">
-        <v>31.46</v>
+        <v>33.03300000000001</v>
       </c>
       <c r="G22">
         <v>26.2</v>
@@ -3091,28 +3091,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M22">
-        <v>2.384668</v>
+        <v>2.503901400000001</v>
       </c>
       <c r="N22">
-        <v>2.870434040816332</v>
+        <v>2.751200640816331</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.870434040816332</v>
+        <v>2.751200640816331</v>
       </c>
       <c r="Q22">
-        <v>50.37043404081633</v>
+        <v>50.25120064081633</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1386464779529968</v>
+        <v>0.1398217498258195</v>
       </c>
       <c r="T22">
-        <v>0.7953028499436883</v>
+        <v>0.8053699746265198</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.203703845070396</v>
+        <v>2.09876556673371</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1263771823623974</v>
+        <v>0.1266771823623974</v>
       </c>
       <c r="C23">
-        <v>143.0771966275714</v>
+        <v>140.9632461308457</v>
       </c>
       <c r="D23">
-        <v>149.9101966275715</v>
+        <v>149.3692461308457</v>
       </c>
       <c r="E23">
-        <v>-14.267</v>
+        <v>-12.694</v>
       </c>
       <c r="F23">
-        <v>33.033</v>
+        <v>34.606</v>
       </c>
       <c r="G23">
         <v>26.2</v>
@@ -3173,28 +3173,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M23">
-        <v>2.5039014</v>
+        <v>2.6231348</v>
       </c>
       <c r="N23">
-        <v>2.751200640816332</v>
+        <v>2.631967240816332</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.751200640816332</v>
+        <v>2.631967240816332</v>
       </c>
       <c r="Q23">
-        <v>50.25120064081634</v>
+        <v>50.13196724081633</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1398217498258195</v>
+        <v>0.1410271568748685</v>
       </c>
       <c r="T23">
-        <v>0.8053699746265198</v>
+        <v>0.8156952307114751</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.098765566733711</v>
+        <v>2.003367131882178</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1266771823623974</v>
+        <v>0.1302431823623974</v>
       </c>
       <c r="C24">
-        <v>140.9632461308457</v>
+        <v>133.2468591867004</v>
       </c>
       <c r="D24">
-        <v>149.3692461308457</v>
+        <v>143.2258591867004</v>
       </c>
       <c r="E24">
-        <v>-12.694</v>
+        <v>-11.121</v>
       </c>
       <c r="F24">
-        <v>34.606</v>
+        <v>36.179</v>
       </c>
       <c r="G24">
         <v>26.2</v>
@@ -3255,45 +3255,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M24">
-        <v>2.6231348</v>
+        <v>3.25611</v>
       </c>
       <c r="N24">
-        <v>2.631967240816332</v>
+        <v>1.998992040816332</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.631967240816332</v>
+        <v>1.998992040816332</v>
       </c>
       <c r="Q24">
-        <v>50.13196724081633</v>
+        <v>49.49899204081633</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1410271568748685</v>
+        <v>0.1422638731979187</v>
       </c>
       <c r="T24">
-        <v>0.8156952307114751</v>
+        <v>0.8262886752661697</v>
       </c>
       <c r="U24">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.003367131882178</v>
+        <v>1.613920303925952</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1302431823623974</v>
+        <v>0.1306851823623974</v>
       </c>
       <c r="C25">
-        <v>133.2468591867004</v>
+        <v>130.9474175952439</v>
       </c>
       <c r="D25">
-        <v>143.2258591867004</v>
+        <v>142.4994175952439</v>
       </c>
       <c r="E25">
-        <v>-11.121</v>
+        <v>-9.547999999999995</v>
       </c>
       <c r="F25">
-        <v>36.179</v>
+        <v>37.752</v>
       </c>
       <c r="G25">
         <v>26.2</v>
@@ -3337,28 +3337,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M25">
-        <v>3.25611</v>
+        <v>3.39768</v>
       </c>
       <c r="N25">
-        <v>1.998992040816332</v>
+        <v>1.857422040816332</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.998992040816332</v>
+        <v>1.857422040816332</v>
       </c>
       <c r="Q25">
-        <v>49.49899204081633</v>
+        <v>49.35742204081633</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1422638731979187</v>
+        <v>0.143533134687365</v>
       </c>
       <c r="T25">
-        <v>0.8262886752661697</v>
+        <v>0.8371608946775667</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.613920303925952</v>
+        <v>1.546673624595704</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1306851823623974</v>
+        <v>0.1453271823623974</v>
       </c>
       <c r="C26">
-        <v>130.9474175952439</v>
+        <v>108.8759817245539</v>
       </c>
       <c r="D26">
-        <v>142.4994175952439</v>
+        <v>122.0009817245539</v>
       </c>
       <c r="E26">
-        <v>-9.547999999999995</v>
+        <v>-7.974999999999994</v>
       </c>
       <c r="F26">
-        <v>37.752</v>
+        <v>39.325</v>
       </c>
       <c r="G26">
         <v>26.2</v>
@@ -3419,45 +3419,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M26">
-        <v>3.39768</v>
+        <v>5.772910000000001</v>
       </c>
       <c r="N26">
-        <v>1.857422040816332</v>
+        <v>-0.5178079591836688</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P26">
-        <v>1.857422040816332</v>
+        <v>-0.5178079591836688</v>
       </c>
       <c r="Q26">
-        <v>49.35742204081633</v>
+        <v>46.98219204081633</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.143533134687365</v>
+        <v>0.1448362431498632</v>
       </c>
       <c r="T26">
-        <v>0.8371608946775667</v>
+        <v>0.8483230399399342</v>
       </c>
       <c r="U26">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.546673624595704</v>
+        <v>0.9103038226503326</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1453271823623974</v>
+        <v>0.1463371823623974</v>
       </c>
       <c r="C27">
-        <v>108.8759817245539</v>
+        <v>106.104300206264</v>
       </c>
       <c r="D27">
-        <v>122.0009817245539</v>
+        <v>120.8023002062641</v>
       </c>
       <c r="E27">
-        <v>-7.974999999999994</v>
+        <v>-6.401999999999994</v>
       </c>
       <c r="F27">
-        <v>39.325</v>
+        <v>40.898</v>
       </c>
       <c r="G27">
         <v>26.2</v>
@@ -3501,28 +3501,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M27">
-        <v>5.772910000000001</v>
+        <v>6.003826400000001</v>
       </c>
       <c r="N27">
-        <v>-0.5178079591836688</v>
+        <v>-0.7487243591836688</v>
       </c>
       <c r="O27">
         <v>-0</v>
       </c>
       <c r="P27">
-        <v>-0.5178079591836688</v>
+        <v>-0.7487243591836688</v>
       </c>
       <c r="Q27">
-        <v>46.98219204081633</v>
+        <v>46.75127564081633</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1448362431498632</v>
+        <v>0.1461745707599965</v>
       </c>
       <c r="T27">
-        <v>0.8483230399399342</v>
+        <v>0.8597868648039874</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.9103038226503326</v>
+        <v>0.8752921371637813</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1463371823623974</v>
+        <v>0.1473471823623974</v>
       </c>
       <c r="C28">
-        <v>106.104300206264</v>
+        <v>103.3559440339121</v>
       </c>
       <c r="D28">
-        <v>120.8023002062641</v>
+        <v>119.6269440339121</v>
       </c>
       <c r="E28">
-        <v>-6.401999999999994</v>
+        <v>-4.828999999999994</v>
       </c>
       <c r="F28">
-        <v>40.898</v>
+        <v>42.471</v>
       </c>
       <c r="G28">
         <v>26.2</v>
@@ -3583,28 +3583,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M28">
-        <v>6.003826400000001</v>
+        <v>6.234742800000001</v>
       </c>
       <c r="N28">
-        <v>-0.7487243591836688</v>
+        <v>-0.9796407591836687</v>
       </c>
       <c r="O28">
         <v>-0</v>
       </c>
       <c r="P28">
-        <v>-0.7487243591836688</v>
+        <v>-0.9796407591836687</v>
       </c>
       <c r="Q28">
-        <v>46.75127564081633</v>
+        <v>46.52035924081633</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1461745707599965</v>
+        <v>0.1475495648799965</v>
       </c>
       <c r="T28">
-        <v>0.8597868648039874</v>
+        <v>0.8715647670615763</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.8752921371637813</v>
+        <v>0.8428739098614191</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1473471823623974</v>
+        <v>0.1483571823623974</v>
       </c>
       <c r="C29">
-        <v>103.3559440339121</v>
+        <v>100.6302389301722</v>
       </c>
       <c r="D29">
-        <v>119.6269440339121</v>
+        <v>118.4742389301722</v>
       </c>
       <c r="E29">
-        <v>-4.828999999999994</v>
+        <v>-3.255999999999993</v>
       </c>
       <c r="F29">
-        <v>42.471</v>
+        <v>44.044</v>
       </c>
       <c r="G29">
         <v>26.2</v>
@@ -3665,28 +3665,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M29">
-        <v>6.234742800000001</v>
+        <v>6.465659200000001</v>
       </c>
       <c r="N29">
-        <v>-0.9796407591836687</v>
+        <v>-1.210557159183669</v>
       </c>
       <c r="O29">
         <v>-0</v>
       </c>
       <c r="P29">
-        <v>-0.9796407591836687</v>
+        <v>-1.210557159183669</v>
       </c>
       <c r="Q29">
-        <v>46.52035924081633</v>
+        <v>46.28944284081633</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1475495648799965</v>
+        <v>0.1489627532811075</v>
       </c>
       <c r="T29">
-        <v>0.8715647670615763</v>
+        <v>0.8836698332707648</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.8428739098614191</v>
+        <v>0.8127712702235113</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1483571823623974</v>
+        <v>0.1650271823623974</v>
       </c>
       <c r="C30">
-        <v>100.6302389301722</v>
+        <v>82.80065317432658</v>
       </c>
       <c r="D30">
-        <v>118.4742389301722</v>
+        <v>102.2176531743266</v>
       </c>
       <c r="E30">
-        <v>-3.255999999999993</v>
+        <v>-1.682999999999986</v>
       </c>
       <c r="F30">
-        <v>44.044</v>
+        <v>45.61700000000001</v>
       </c>
       <c r="G30">
         <v>26.2</v>
@@ -3747,45 +3747,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M30">
-        <v>6.465659200000001</v>
+        <v>9.159893600000002</v>
       </c>
       <c r="N30">
-        <v>-1.210557159183669</v>
+        <v>-3.904791559183669</v>
       </c>
       <c r="O30">
         <v>-0</v>
       </c>
       <c r="P30">
-        <v>-1.210557159183669</v>
+        <v>-3.904791559183669</v>
       </c>
       <c r="Q30">
-        <v>46.28944284081633</v>
+        <v>43.59520844081633</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1489627532811075</v>
+        <v>0.1504157498061935</v>
       </c>
       <c r="T30">
-        <v>0.8836698332707648</v>
+        <v>0.896115887260494</v>
       </c>
       <c r="U30">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y30">
-        <v>0.8127712702235113</v>
+        <v>0.573707760187993</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1650271823623974</v>
+        <v>0.1665771823623974</v>
       </c>
       <c r="C31">
-        <v>82.80065317432661</v>
+        <v>79.93993301337636</v>
       </c>
       <c r="D31">
-        <v>102.2176531743266</v>
+        <v>100.9299330133764</v>
       </c>
       <c r="E31">
-        <v>-1.683</v>
+        <v>-0.1099999999999923</v>
       </c>
       <c r="F31">
-        <v>45.617</v>
+        <v>47.19</v>
       </c>
       <c r="G31">
         <v>26.2</v>
@@ -3829,28 +3829,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M31">
-        <v>9.1598936</v>
+        <v>9.475752000000002</v>
       </c>
       <c r="N31">
-        <v>-3.904791559183668</v>
+        <v>-4.220649959183669</v>
       </c>
       <c r="O31">
         <v>-0</v>
       </c>
       <c r="P31">
-        <v>-3.904791559183668</v>
+        <v>-4.220649959183669</v>
       </c>
       <c r="Q31">
-        <v>43.59520844081634</v>
+        <v>43.27935004081633</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1504157498061935</v>
+        <v>0.1519102605177106</v>
       </c>
       <c r="T31">
-        <v>0.8961158872604938</v>
+        <v>0.9089175427927867</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5737077601879931</v>
+        <v>0.5545841681817265</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1665771823623974</v>
+        <v>0.1681271823623974</v>
       </c>
       <c r="C32">
-        <v>79.93993301337636</v>
+        <v>77.11125414959717</v>
       </c>
       <c r="D32">
-        <v>100.9299330133764</v>
+        <v>99.67425414959718</v>
       </c>
       <c r="E32">
-        <v>-0.1099999999999923</v>
+        <v>1.463000000000008</v>
       </c>
       <c r="F32">
-        <v>47.19</v>
+        <v>48.76300000000001</v>
       </c>
       <c r="G32">
         <v>26.2</v>
@@ -3911,28 +3911,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M32">
-        <v>9.475752000000002</v>
+        <v>9.791610400000001</v>
       </c>
       <c r="N32">
-        <v>-4.220649959183669</v>
+        <v>-4.536508359183669</v>
       </c>
       <c r="O32">
         <v>-0</v>
       </c>
       <c r="P32">
-        <v>-4.220649959183669</v>
+        <v>-4.536508359183669</v>
       </c>
       <c r="Q32">
-        <v>43.27935004081633</v>
+        <v>42.96349164081633</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1519102605177106</v>
+        <v>0.1534480903802861</v>
       </c>
       <c r="T32">
-        <v>0.9089175427927867</v>
+        <v>0.9220902608042763</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5545841681817265</v>
+        <v>0.5366943563048967</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1681271823623974</v>
+        <v>0.1696771823623974</v>
       </c>
       <c r="C33">
-        <v>77.11125414959717</v>
+        <v>74.31343539185394</v>
       </c>
       <c r="D33">
-        <v>99.67425414959718</v>
+        <v>98.44943539185395</v>
       </c>
       <c r="E33">
-        <v>1.463000000000008</v>
+        <v>3.036000000000008</v>
       </c>
       <c r="F33">
-        <v>48.76300000000001</v>
+        <v>50.33600000000001</v>
       </c>
       <c r="G33">
         <v>26.2</v>
@@ -3993,28 +3993,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M33">
-        <v>9.791610400000001</v>
+        <v>10.1074688</v>
       </c>
       <c r="N33">
-        <v>-4.536508359183669</v>
+        <v>-4.852366759183669</v>
       </c>
       <c r="O33">
         <v>-0</v>
       </c>
       <c r="P33">
-        <v>-4.536508359183669</v>
+        <v>-4.852366759183669</v>
       </c>
       <c r="Q33">
-        <v>42.96349164081633</v>
+        <v>42.64763324081633</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1534480903802861</v>
+        <v>0.1550311505329374</v>
       </c>
       <c r="T33">
-        <v>0.9220902608042763</v>
+        <v>0.9356504116984569</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5366943563048967</v>
+        <v>0.5199226576703686</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1696771823623974</v>
+        <v>0.1712271823623974</v>
       </c>
       <c r="C34">
-        <v>74.31343539185394</v>
+        <v>71.54535290315849</v>
       </c>
       <c r="D34">
-        <v>98.44943539185395</v>
+        <v>97.25435290315849</v>
       </c>
       <c r="E34">
-        <v>3.036000000000008</v>
+        <v>4.609000000000009</v>
       </c>
       <c r="F34">
-        <v>50.33600000000001</v>
+        <v>51.90900000000001</v>
       </c>
       <c r="G34">
         <v>26.2</v>
@@ -4075,28 +4075,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M34">
-        <v>10.1074688</v>
+        <v>10.4233272</v>
       </c>
       <c r="N34">
-        <v>-4.852366759183669</v>
+        <v>-5.168225159183669</v>
       </c>
       <c r="O34">
         <v>-0</v>
       </c>
       <c r="P34">
-        <v>-4.852366759183669</v>
+        <v>-5.168225159183669</v>
       </c>
       <c r="Q34">
-        <v>42.64763324081633</v>
+        <v>42.33177484081633</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1550311505329374</v>
+        <v>0.1566614662125335</v>
       </c>
       <c r="T34">
-        <v>0.9356504116984569</v>
+        <v>0.9496153432163443</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5199226576703686</v>
+        <v>0.5041674256197515</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1712271823623974</v>
+        <v>0.1846771823623974</v>
       </c>
       <c r="C35">
-        <v>71.54535290315849</v>
+        <v>60.70426543720365</v>
       </c>
       <c r="D35">
-        <v>97.25435290315849</v>
+        <v>87.98626543720366</v>
       </c>
       <c r="E35">
-        <v>4.609000000000009</v>
+        <v>6.182000000000009</v>
       </c>
       <c r="F35">
-        <v>51.90900000000001</v>
+        <v>53.48200000000001</v>
       </c>
       <c r="G35">
         <v>26.2</v>
@@ -4157,45 +4157,45 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M35">
-        <v>10.4233272</v>
+        <v>12.6110556</v>
       </c>
       <c r="N35">
-        <v>-5.168225159183669</v>
+        <v>-7.35595355918367</v>
       </c>
       <c r="O35">
         <v>-0</v>
       </c>
       <c r="P35">
-        <v>-5.168225159183669</v>
+        <v>-7.35595355918367</v>
       </c>
       <c r="Q35">
-        <v>42.33177484081633</v>
+        <v>40.14404644081633</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1566614662125335</v>
+        <v>0.1583411853975718</v>
       </c>
       <c r="T35">
-        <v>0.9496153432163443</v>
+        <v>0.9640034544771979</v>
       </c>
       <c r="U35">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.5041674256197515</v>
+        <v>0.4167059608250662</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1846771823623974</v>
+        <v>0.1865771823623974</v>
       </c>
       <c r="C36">
-        <v>60.70426543720365</v>
+        <v>57.96252042710874</v>
       </c>
       <c r="D36">
-        <v>87.98626543720366</v>
+        <v>86.81752042710875</v>
       </c>
       <c r="E36">
-        <v>6.182000000000009</v>
+        <v>7.75500000000001</v>
       </c>
       <c r="F36">
-        <v>53.48200000000001</v>
+        <v>55.05500000000001</v>
       </c>
       <c r="G36">
         <v>26.2</v>
@@ -4239,28 +4239,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M36">
-        <v>12.6110556</v>
+        <v>12.981969</v>
       </c>
       <c r="N36">
-        <v>-7.35595355918367</v>
+        <v>-7.726866959183671</v>
       </c>
       <c r="O36">
         <v>-0</v>
       </c>
       <c r="P36">
-        <v>-7.35595355918367</v>
+        <v>-7.726866959183671</v>
       </c>
       <c r="Q36">
-        <v>40.14404644081633</v>
+        <v>39.77313304081633</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1583411853975718</v>
+        <v>0.1600725882498422</v>
       </c>
       <c r="T36">
-        <v>0.9640034544771979</v>
+        <v>0.9788342768537702</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4167059608250662</v>
+        <v>0.4048000762300643</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1865771823623974</v>
+        <v>0.1884771823623974</v>
       </c>
       <c r="C37">
-        <v>57.96252042710874</v>
+        <v>55.25141788773464</v>
       </c>
       <c r="D37">
-        <v>86.81752042710875</v>
+        <v>85.67941788773464</v>
       </c>
       <c r="E37">
-        <v>7.75500000000001</v>
+        <v>9.32800000000001</v>
       </c>
       <c r="F37">
-        <v>55.05500000000001</v>
+        <v>56.62800000000001</v>
       </c>
       <c r="G37">
         <v>26.2</v>
@@ -4321,28 +4321,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M37">
-        <v>12.981969</v>
+        <v>13.3528824</v>
       </c>
       <c r="N37">
-        <v>-7.726866959183671</v>
+        <v>-8.09778035918367</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-7.726866959183671</v>
+        <v>-8.09778035918367</v>
       </c>
       <c r="Q37">
-        <v>39.77313304081633</v>
+        <v>39.40221964081633</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1600725882498422</v>
+        <v>0.1618580974412459</v>
       </c>
       <c r="T37">
-        <v>0.9788342768537702</v>
+        <v>0.9941285624296103</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.4048000762300643</v>
+        <v>0.3935556296681181</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1884771823623974</v>
+        <v>0.1903771823623974</v>
       </c>
       <c r="C38">
-        <v>55.25141788773465</v>
+        <v>52.56976832354155</v>
       </c>
       <c r="D38">
-        <v>85.67941788773464</v>
+        <v>84.57076832354154</v>
       </c>
       <c r="E38">
-        <v>9.328000000000003</v>
+        <v>10.901</v>
       </c>
       <c r="F38">
-        <v>56.628</v>
+        <v>58.201</v>
       </c>
       <c r="G38">
         <v>26.2</v>
@@ -4403,28 +4403,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M38">
-        <v>13.3528824</v>
+        <v>13.7237958</v>
       </c>
       <c r="N38">
-        <v>-8.097780359183668</v>
+        <v>-8.468693759183669</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-8.097780359183668</v>
+        <v>-8.468693759183669</v>
       </c>
       <c r="Q38">
-        <v>39.40221964081633</v>
+        <v>39.03130624081633</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1618580974412459</v>
+        <v>0.1637002894641229</v>
       </c>
       <c r="T38">
-        <v>0.9941285624296103</v>
+        <v>1.009908380880874</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3935556296681181</v>
+        <v>0.3829189910284392</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1903771823623974</v>
+        <v>0.1922771823623974</v>
       </c>
       <c r="C39">
-        <v>52.56976832354155</v>
+        <v>49.91644301848385</v>
       </c>
       <c r="D39">
-        <v>84.57076832354154</v>
+        <v>83.49044301848386</v>
       </c>
       <c r="E39">
-        <v>10.901</v>
+        <v>12.47400000000001</v>
       </c>
       <c r="F39">
-        <v>58.201</v>
+        <v>59.77400000000001</v>
       </c>
       <c r="G39">
         <v>26.2</v>
@@ -4485,28 +4485,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M39">
-        <v>13.7237958</v>
+        <v>14.0947092</v>
       </c>
       <c r="N39">
-        <v>-8.468693759183669</v>
+        <v>-8.83960715918367</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-8.468693759183669</v>
+        <v>-8.83960715918367</v>
       </c>
       <c r="Q39">
-        <v>39.03130624081633</v>
+        <v>38.66039284081633</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1637002894641229</v>
+        <v>0.1656019070361248</v>
       </c>
       <c r="T39">
-        <v>1.009908380880874</v>
+        <v>1.026197225733791</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3829189910284392</v>
+        <v>0.3728421754750593</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1922771823623974</v>
+        <v>0.1941771823623974</v>
       </c>
       <c r="C40">
-        <v>49.91644301848385</v>
+        <v>47.29037020292292</v>
       </c>
       <c r="D40">
-        <v>83.49044301848386</v>
+        <v>82.43737020292292</v>
       </c>
       <c r="E40">
-        <v>12.47400000000001</v>
+        <v>14.04700000000001</v>
       </c>
       <c r="F40">
-        <v>59.77400000000001</v>
+        <v>61.34700000000001</v>
       </c>
       <c r="G40">
         <v>26.2</v>
@@ -4567,28 +4567,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M40">
-        <v>14.0947092</v>
+        <v>14.4656226</v>
       </c>
       <c r="N40">
-        <v>-8.83960715918367</v>
+        <v>-9.210520559183671</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-8.83960715918367</v>
+        <v>-9.210520559183671</v>
       </c>
       <c r="Q40">
-        <v>38.66039284081633</v>
+        <v>38.28947944081633</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1656019070361248</v>
+        <v>0.1675658727252416</v>
       </c>
       <c r="T40">
-        <v>1.026197225733791</v>
+        <v>1.04302013107369</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3728421754750593</v>
+        <v>0.3632821196936474</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1941771823623974</v>
+        <v>0.1960771823623974</v>
       </c>
       <c r="C41">
-        <v>47.29037020292292</v>
+        <v>44.69053150700869</v>
       </c>
       <c r="D41">
-        <v>82.43737020292292</v>
+        <v>81.4105315070087</v>
       </c>
       <c r="E41">
-        <v>14.04700000000001</v>
+        <v>15.62000000000001</v>
       </c>
       <c r="F41">
-        <v>61.34700000000001</v>
+        <v>62.92000000000001</v>
       </c>
       <c r="G41">
         <v>26.2</v>
@@ -4649,28 +4649,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M41">
-        <v>14.4656226</v>
+        <v>14.836536</v>
       </c>
       <c r="N41">
-        <v>-9.210520559183671</v>
+        <v>-9.58143395918367</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-9.210520559183671</v>
+        <v>-9.58143395918367</v>
       </c>
       <c r="Q41">
-        <v>38.28947944081633</v>
+        <v>37.91856604081633</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1675658727252416</v>
+        <v>0.169595303937329</v>
       </c>
       <c r="T41">
-        <v>1.04302013107369</v>
+        <v>1.060403799924918</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3632821196936474</v>
+        <v>0.3542000667013062</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1960771823623974</v>
+        <v>0.1979771823623974</v>
       </c>
       <c r="C42">
-        <v>44.69053150700869</v>
+        <v>42.11595867586064</v>
       </c>
       <c r="D42">
-        <v>81.4105315070087</v>
+        <v>80.40895867586065</v>
       </c>
       <c r="E42">
-        <v>15.62000000000001</v>
+        <v>17.19300000000001</v>
       </c>
       <c r="F42">
-        <v>62.92000000000001</v>
+        <v>64.49300000000001</v>
       </c>
       <c r="G42">
         <v>26.2</v>
@@ -4731,28 +4731,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M42">
-        <v>14.836536</v>
+        <v>15.2074494</v>
       </c>
       <c r="N42">
-        <v>-9.58143395918367</v>
+        <v>-9.952347359183671</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-9.58143395918367</v>
+        <v>-9.952347359183671</v>
       </c>
       <c r="Q42">
-        <v>37.91856604081633</v>
+        <v>37.54765264081633</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.169595303937329</v>
+        <v>0.1716935294277922</v>
       </c>
       <c r="T42">
-        <v>1.060403799924918</v>
+        <v>1.078376745686357</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3542000667013062</v>
+        <v>0.3455610406842012</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1979771823623974</v>
+        <v>0.1998771823623974</v>
       </c>
       <c r="C43">
-        <v>42.11595867586064</v>
+        <v>39.56573052427512</v>
       </c>
       <c r="D43">
-        <v>80.40895867586065</v>
+        <v>79.43173052427514</v>
       </c>
       <c r="E43">
-        <v>17.19300000000001</v>
+        <v>18.76600000000002</v>
       </c>
       <c r="F43">
-        <v>64.49300000000001</v>
+        <v>66.06600000000002</v>
       </c>
       <c r="G43">
         <v>26.2</v>
@@ -4813,28 +4813,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M43">
-        <v>15.2074494</v>
+        <v>15.5783628</v>
       </c>
       <c r="N43">
-        <v>-9.952347359183671</v>
+        <v>-10.32326075918367</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-9.952347359183671</v>
+        <v>-10.32326075918367</v>
       </c>
       <c r="Q43">
-        <v>37.54765264081633</v>
+        <v>37.17673924081633</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1716935294277922</v>
+        <v>0.1738641075213748</v>
       </c>
       <c r="T43">
-        <v>1.078376745686357</v>
+        <v>1.096969448198191</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3455610406842012</v>
+        <v>0.3373333968583869</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1998771823623974</v>
+        <v>0.2017771823623974</v>
       </c>
       <c r="C44">
-        <v>39.56573052427514</v>
+        <v>37.03897011082748</v>
       </c>
       <c r="D44">
-        <v>79.43173052427514</v>
+        <v>78.47797011082748</v>
       </c>
       <c r="E44">
-        <v>18.76600000000001</v>
+        <v>20.33900000000001</v>
       </c>
       <c r="F44">
-        <v>66.066</v>
+        <v>67.63900000000001</v>
       </c>
       <c r="G44">
         <v>26.2</v>
@@ -4895,28 +4895,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M44">
-        <v>15.5783628</v>
+        <v>15.9492762</v>
       </c>
       <c r="N44">
-        <v>-10.32326075918367</v>
+        <v>-10.69417415918367</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-10.32326075918367</v>
+        <v>-10.69417415918367</v>
       </c>
       <c r="Q44">
-        <v>37.17673924081633</v>
+        <v>36.80582584081633</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1738641075213748</v>
+        <v>0.17611084624982</v>
       </c>
       <c r="T44">
-        <v>1.096969448198191</v>
+        <v>1.116214526236756</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3373333968583869</v>
+        <v>0.32948843414075</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2017771823623974</v>
+        <v>0.2036771823623974</v>
       </c>
       <c r="C45">
-        <v>37.03897011082748</v>
+        <v>34.5348421131466</v>
       </c>
       <c r="D45">
-        <v>78.47797011082748</v>
+        <v>77.5468421131466</v>
       </c>
       <c r="E45">
-        <v>20.33900000000001</v>
+        <v>21.91200000000001</v>
       </c>
       <c r="F45">
-        <v>67.63900000000001</v>
+        <v>69.212</v>
       </c>
       <c r="G45">
         <v>26.2</v>
@@ -4977,28 +4977,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M45">
-        <v>15.9492762</v>
+        <v>16.3201896</v>
       </c>
       <c r="N45">
-        <v>-10.69417415918367</v>
+        <v>-11.06508755918367</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-10.69417415918367</v>
+        <v>-11.06508755918367</v>
       </c>
       <c r="Q45">
-        <v>36.80582584081633</v>
+        <v>36.43491244081633</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.17611084624982</v>
+        <v>0.1784378256471382</v>
       </c>
       <c r="T45">
-        <v>1.116214526236756</v>
+        <v>1.136146928490983</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.32948843414075</v>
+        <v>0.3220000606375512</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2036771823623974</v>
+        <v>0.2055771823623974</v>
       </c>
       <c r="C46">
-        <v>34.5348421131466</v>
+        <v>32.05255038785052</v>
       </c>
       <c r="D46">
-        <v>77.5468421131466</v>
+        <v>76.63755038785052</v>
       </c>
       <c r="E46">
-        <v>21.91200000000001</v>
+        <v>23.48500000000001</v>
       </c>
       <c r="F46">
-        <v>69.212</v>
+        <v>70.78500000000001</v>
       </c>
       <c r="G46">
         <v>26.2</v>
@@ -5059,28 +5059,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M46">
-        <v>16.3201896</v>
+        <v>16.691103</v>
       </c>
       <c r="N46">
-        <v>-11.06508755918367</v>
+        <v>-11.43600095918367</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-11.06508755918367</v>
+        <v>-11.43600095918367</v>
       </c>
       <c r="Q46">
-        <v>36.43491244081633</v>
+        <v>36.06399904081633</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1784378256471382</v>
+        <v>0.1808494224770862</v>
       </c>
       <c r="T46">
-        <v>1.136146928490983</v>
+        <v>1.156804145372637</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3220000606375512</v>
+        <v>0.3148445037344945</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2055771823623974</v>
+        <v>0.2074771823623974</v>
       </c>
       <c r="C47">
-        <v>32.05255038785052</v>
+        <v>29.59133570016111</v>
       </c>
       <c r="D47">
-        <v>76.63755038785052</v>
+        <v>75.74933570016111</v>
       </c>
       <c r="E47">
-        <v>23.48500000000001</v>
+        <v>25.05800000000001</v>
       </c>
       <c r="F47">
-        <v>70.78500000000001</v>
+        <v>72.358</v>
       </c>
       <c r="G47">
         <v>26.2</v>
@@ -5141,28 +5141,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M47">
-        <v>16.691103</v>
+        <v>17.0620164</v>
       </c>
       <c r="N47">
-        <v>-11.43600095918367</v>
+        <v>-11.80691435918367</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-11.43600095918367</v>
+        <v>-11.80691435918367</v>
       </c>
       <c r="Q47">
-        <v>36.06399904081633</v>
+        <v>35.69308564081634</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1808494224770862</v>
+        <v>0.1833503377081434</v>
       </c>
       <c r="T47">
-        <v>1.156804145372637</v>
+        <v>1.17822644436102</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3148445037344945</v>
+        <v>0.3080000580011359</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2074771823623974</v>
+        <v>0.2093771823623974</v>
       </c>
       <c r="C48">
-        <v>29.59133570016111</v>
+        <v>27.15047360958975</v>
       </c>
       <c r="D48">
-        <v>75.74933570016111</v>
+        <v>74.88147360958976</v>
       </c>
       <c r="E48">
-        <v>25.05800000000001</v>
+        <v>26.63100000000001</v>
       </c>
       <c r="F48">
-        <v>72.358</v>
+        <v>73.93100000000001</v>
       </c>
       <c r="G48">
         <v>26.2</v>
@@ -5223,28 +5223,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M48">
-        <v>17.0620164</v>
+        <v>17.4329298</v>
       </c>
       <c r="N48">
-        <v>-11.80691435918367</v>
+        <v>-12.17782775918367</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-11.80691435918367</v>
+        <v>-12.17782775918367</v>
       </c>
       <c r="Q48">
-        <v>35.69308564081634</v>
+        <v>35.32217224081633</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1833503377081434</v>
+        <v>0.185945627098863</v>
       </c>
       <c r="T48">
-        <v>1.17822644436102</v>
+        <v>1.200457131990473</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3080000580011359</v>
+        <v>0.3014468652777075</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2093771823623974</v>
+        <v>0.2112771823623974</v>
       </c>
       <c r="C49">
-        <v>27.15047360958975</v>
+        <v>24.72927249931968</v>
       </c>
       <c r="D49">
-        <v>74.88147360958976</v>
+        <v>74.03327249931968</v>
       </c>
       <c r="E49">
-        <v>26.63100000000001</v>
+        <v>28.20400000000001</v>
       </c>
       <c r="F49">
-        <v>73.93100000000001</v>
+        <v>75.504</v>
       </c>
       <c r="G49">
         <v>26.2</v>
@@ -5305,28 +5305,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M49">
-        <v>17.4329298</v>
+        <v>17.8038432</v>
       </c>
       <c r="N49">
-        <v>-12.17782775918367</v>
+        <v>-12.54874115918367</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-12.17782775918367</v>
+        <v>-12.54874115918367</v>
       </c>
       <c r="Q49">
-        <v>35.32217224081633</v>
+        <v>34.95125884081633</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.185945627098863</v>
+        <v>0.1886407353123027</v>
       </c>
       <c r="T49">
-        <v>1.200457131990473</v>
+        <v>1.223542846067213</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3014468652777075</v>
+        <v>0.2951667222510885</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2112771823623974</v>
+        <v>0.2131771823623974</v>
       </c>
       <c r="C50">
-        <v>24.72927249931969</v>
+        <v>22.32707173801784</v>
       </c>
       <c r="D50">
-        <v>74.03327249931969</v>
+        <v>73.20407173801783</v>
       </c>
       <c r="E50">
-        <v>28.20400000000001</v>
+        <v>29.777</v>
       </c>
       <c r="F50">
-        <v>75.504</v>
+        <v>77.077</v>
       </c>
       <c r="G50">
         <v>26.2</v>
@@ -5387,28 +5387,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M50">
-        <v>17.8038432</v>
+        <v>18.1747566</v>
       </c>
       <c r="N50">
-        <v>-12.54874115918367</v>
+        <v>-12.91965455918367</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-12.54874115918367</v>
+        <v>-12.91965455918367</v>
       </c>
       <c r="Q50">
-        <v>34.95125884081633</v>
+        <v>34.58034544081633</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1886407353123027</v>
+        <v>0.1914415340439165</v>
       </c>
       <c r="T50">
-        <v>1.223542846067213</v>
+        <v>1.247533882264609</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2951667222510885</v>
+        <v>0.2891429115929031</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2131771823623974</v>
+        <v>0.2150771823623974</v>
       </c>
       <c r="C51">
-        <v>22.32707173801784</v>
+        <v>19.94323996380913</v>
       </c>
       <c r="D51">
-        <v>73.20407173801783</v>
+        <v>72.39323996380914</v>
       </c>
       <c r="E51">
-        <v>29.777</v>
+        <v>31.35000000000001</v>
       </c>
       <c r="F51">
-        <v>77.077</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="G51">
         <v>26.2</v>
@@ -5469,28 +5469,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M51">
-        <v>18.1747566</v>
+        <v>18.54567</v>
       </c>
       <c r="N51">
-        <v>-12.91965455918367</v>
+        <v>-13.29056795918367</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-12.91965455918367</v>
+        <v>-13.29056795918367</v>
       </c>
       <c r="Q51">
-        <v>34.58034544081633</v>
+        <v>34.20943204081633</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1914415340439165</v>
+        <v>0.1943543647247948</v>
       </c>
       <c r="T51">
-        <v>1.247533882264609</v>
+        <v>1.272484559909901</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2891429115929031</v>
+        <v>0.2833600533610451</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2150771823623974</v>
+        <v>0.2169771823623974</v>
       </c>
       <c r="C52">
-        <v>19.94323996380913</v>
+        <v>17.57717348104498</v>
       </c>
       <c r="D52">
-        <v>72.39323996380914</v>
+        <v>71.60017348104499</v>
       </c>
       <c r="E52">
-        <v>31.35000000000001</v>
+        <v>32.92300000000002</v>
       </c>
       <c r="F52">
-        <v>78.65000000000001</v>
+        <v>80.22300000000001</v>
       </c>
       <c r="G52">
         <v>26.2</v>
@@ -5551,28 +5551,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M52">
-        <v>18.54567</v>
+        <v>18.9165834</v>
       </c>
       <c r="N52">
-        <v>-13.29056795918367</v>
+        <v>-13.66148135918367</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-13.29056795918367</v>
+        <v>-13.66148135918367</v>
       </c>
       <c r="Q52">
-        <v>34.20943204081633</v>
+        <v>33.83851864081633</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1943543647247948</v>
+        <v>0.1973860864538723</v>
       </c>
       <c r="T52">
-        <v>1.272484559909901</v>
+        <v>1.298453632561124</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2833600533610451</v>
+        <v>0.2778039738833774</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2169771823623974</v>
+        <v>0.2188771823623974</v>
       </c>
       <c r="C53">
-        <v>17.57717348104498</v>
+        <v>15.22829476130975</v>
       </c>
       <c r="D53">
-        <v>71.60017348104499</v>
+        <v>70.82429476130976</v>
       </c>
       <c r="E53">
-        <v>32.92300000000002</v>
+        <v>34.49600000000001</v>
       </c>
       <c r="F53">
-        <v>80.22300000000001</v>
+        <v>81.79600000000001</v>
       </c>
       <c r="G53">
         <v>26.2</v>
@@ -5633,28 +5633,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M53">
-        <v>18.9165834</v>
+        <v>19.2874968</v>
       </c>
       <c r="N53">
-        <v>-13.66148135918367</v>
+        <v>-14.03239475918367</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-13.66148135918367</v>
+        <v>-14.03239475918367</v>
       </c>
       <c r="Q53">
-        <v>33.83851864081633</v>
+        <v>33.46760524081633</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1973860864538723</v>
+        <v>0.2005441299216613</v>
       </c>
       <c r="T53">
-        <v>1.298453632561124</v>
+        <v>1.325504749906147</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2778039738833774</v>
+        <v>0.2724615897702356</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2188771823623974</v>
+        <v>0.2207771823623974</v>
       </c>
       <c r="C54">
-        <v>15.22829476130975</v>
+        <v>12.89605104084386</v>
       </c>
       <c r="D54">
-        <v>70.82429476130976</v>
+        <v>70.06505104084387</v>
       </c>
       <c r="E54">
-        <v>34.49600000000001</v>
+        <v>36.06900000000002</v>
       </c>
       <c r="F54">
-        <v>81.79600000000001</v>
+        <v>83.36900000000001</v>
       </c>
       <c r="G54">
         <v>26.2</v>
@@ -5715,28 +5715,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M54">
-        <v>19.2874968</v>
+        <v>19.65841020000001</v>
       </c>
       <c r="N54">
-        <v>-14.03239475918367</v>
+        <v>-14.40330815918367</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-14.03239475918367</v>
+        <v>-14.40330815918367</v>
       </c>
       <c r="Q54">
-        <v>33.46760524081633</v>
+        <v>33.09669184081633</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2005441299216613</v>
+        <v>0.2038365582178668</v>
       </c>
       <c r="T54">
-        <v>1.325504749906147</v>
+        <v>1.353706978627555</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2724615897702356</v>
+        <v>0.2673208050575896</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2207771823623974</v>
+        <v>0.2226771823623974</v>
       </c>
       <c r="C55">
-        <v>12.89605104084386</v>
+        <v>10.57991300722422</v>
       </c>
       <c r="D55">
-        <v>70.06505104084387</v>
+        <v>69.32191300722423</v>
       </c>
       <c r="E55">
-        <v>36.06900000000002</v>
+        <v>37.64200000000001</v>
       </c>
       <c r="F55">
-        <v>83.36900000000001</v>
+        <v>84.94200000000001</v>
       </c>
       <c r="G55">
         <v>26.2</v>
@@ -5797,28 +5797,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M55">
-        <v>19.65841020000001</v>
+        <v>20.0293236</v>
       </c>
       <c r="N55">
-        <v>-14.40330815918367</v>
+        <v>-14.77422155918367</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-14.40330815918367</v>
+        <v>-14.77422155918367</v>
       </c>
       <c r="Q55">
-        <v>33.09669184081633</v>
+        <v>32.72577844081633</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2038365582178668</v>
+        <v>0.2072721355704291</v>
       </c>
       <c r="T55">
-        <v>1.353706978627555</v>
+        <v>1.383135391206414</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2673208050575896</v>
+        <v>0.2623704197787454</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2226771823623974</v>
+        <v>0.2245771823623974</v>
       </c>
       <c r="C56">
-        <v>10.57991300722422</v>
+        <v>8.279373568745314</v>
       </c>
       <c r="D56">
-        <v>69.32191300722423</v>
+        <v>68.59437356874533</v>
       </c>
       <c r="E56">
-        <v>37.64200000000001</v>
+        <v>39.21500000000002</v>
       </c>
       <c r="F56">
-        <v>84.94200000000001</v>
+        <v>86.51500000000001</v>
       </c>
       <c r="G56">
         <v>26.2</v>
@@ -5879,28 +5879,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M56">
-        <v>20.0293236</v>
+        <v>20.400237</v>
       </c>
       <c r="N56">
-        <v>-14.77422155918367</v>
+        <v>-15.14513495918367</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-14.77422155918367</v>
+        <v>-15.14513495918367</v>
       </c>
       <c r="Q56">
-        <v>32.72577844081633</v>
+        <v>32.35486504081633</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2072721355704291</v>
+        <v>0.210860405249772</v>
       </c>
       <c r="T56">
-        <v>1.383135391206414</v>
+        <v>1.413871733233224</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2623704197787454</v>
+        <v>0.2576000485100409</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2245771823623974</v>
+        <v>0.2264771823623974</v>
       </c>
       <c r="C57">
-        <v>8.279373568745314</v>
+        <v>5.993946700488252</v>
       </c>
       <c r="D57">
-        <v>68.59437356874533</v>
+        <v>67.88194670048826</v>
       </c>
       <c r="E57">
-        <v>39.21500000000002</v>
+        <v>40.78800000000001</v>
       </c>
       <c r="F57">
-        <v>86.51500000000001</v>
+        <v>88.08800000000001</v>
       </c>
       <c r="G57">
         <v>26.2</v>
@@ -5961,28 +5961,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M57">
-        <v>20.400237</v>
+        <v>20.7711504</v>
       </c>
       <c r="N57">
-        <v>-15.14513495918367</v>
+        <v>-15.51604835918367</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-15.14513495918367</v>
+        <v>-15.51604835918367</v>
       </c>
       <c r="Q57">
-        <v>32.35486504081633</v>
+        <v>31.98395164081633</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.210860405249772</v>
+        <v>0.2146117780963578</v>
       </c>
       <c r="T57">
-        <v>1.413871733233224</v>
+        <v>1.446005181715797</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2576000485100409</v>
+        <v>0.2530000476437901</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2264771823623974</v>
+        <v>0.2283771823623975</v>
       </c>
       <c r="C58">
-        <v>5.993946700488252</v>
+        <v>3.723166361559137</v>
       </c>
       <c r="D58">
-        <v>67.88194670048826</v>
+        <v>67.18416636155915</v>
       </c>
       <c r="E58">
-        <v>40.78800000000001</v>
+        <v>42.36100000000002</v>
       </c>
       <c r="F58">
-        <v>88.08800000000001</v>
+        <v>89.66100000000002</v>
       </c>
       <c r="G58">
         <v>26.2</v>
@@ -6043,28 +6043,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M58">
-        <v>20.7711504</v>
+        <v>21.14206380000001</v>
       </c>
       <c r="N58">
-        <v>-15.51604835918367</v>
+        <v>-15.88696175918367</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-15.51604835918367</v>
+        <v>-15.88696175918367</v>
       </c>
       <c r="Q58">
-        <v>31.98395164081633</v>
+        <v>31.61303824081633</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2146117780963578</v>
+        <v>0.2185376334009242</v>
       </c>
       <c r="T58">
-        <v>1.446005181715797</v>
+        <v>1.47963320919756</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2530000476437901</v>
+        <v>0.2485614503167061</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2283771823623975</v>
+        <v>0.2302771823623974</v>
       </c>
       <c r="C59">
-        <v>3.723166361559137</v>
+        <v>1.466585478428883</v>
       </c>
       <c r="D59">
-        <v>67.18416636155915</v>
+        <v>66.5005854784289</v>
       </c>
       <c r="E59">
-        <v>42.36100000000002</v>
+        <v>43.93400000000003</v>
       </c>
       <c r="F59">
-        <v>89.66100000000002</v>
+        <v>91.23400000000002</v>
       </c>
       <c r="G59">
         <v>26.2</v>
@@ -6125,28 +6125,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M59">
-        <v>21.14206380000001</v>
+        <v>21.51297720000001</v>
       </c>
       <c r="N59">
-        <v>-15.88696175918367</v>
+        <v>-16.25787515918367</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-15.88696175918367</v>
+        <v>-16.25787515918367</v>
       </c>
       <c r="Q59">
-        <v>31.61303824081633</v>
+        <v>31.24212484081633</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2185376334009242</v>
+        <v>0.2226504341961844</v>
       </c>
       <c r="T59">
-        <v>1.47963320919756</v>
+        <v>1.514862571321311</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2485614503167061</v>
+        <v>0.2442759080698663</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2302771823623974</v>
+        <v>0.2321771823623974</v>
       </c>
       <c r="C60">
-        <v>1.466585478428911</v>
+        <v>-0.7762250102871775</v>
       </c>
       <c r="D60">
-        <v>66.5005854784289</v>
+        <v>65.83077498971282</v>
       </c>
       <c r="E60">
-        <v>43.934</v>
+        <v>45.50700000000001</v>
       </c>
       <c r="F60">
-        <v>91.23399999999999</v>
+        <v>92.807</v>
       </c>
       <c r="G60">
         <v>26.2</v>
@@ -6207,28 +6207,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M60">
-        <v>21.5129772</v>
+        <v>21.8838906</v>
       </c>
       <c r="N60">
-        <v>-16.25787515918367</v>
+        <v>-16.62878855918367</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-16.25787515918367</v>
+        <v>-16.62878855918367</v>
       </c>
       <c r="Q60">
-        <v>31.24212484081633</v>
+        <v>30.87121144081633</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2226504341961843</v>
+        <v>0.2269638594204815</v>
       </c>
       <c r="T60">
-        <v>1.514862571321311</v>
+        <v>1.551810438914514</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2442759080698664</v>
+        <v>0.2401356384415636</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2321771823623974</v>
+        <v>0.2340771823623974</v>
       </c>
       <c r="C61">
-        <v>-0.7762250102871775</v>
+        <v>-3.005677051897663</v>
       </c>
       <c r="D61">
-        <v>65.83077498971282</v>
+        <v>65.17432294810234</v>
       </c>
       <c r="E61">
-        <v>45.50700000000001</v>
+        <v>47.08000000000001</v>
       </c>
       <c r="F61">
-        <v>92.807</v>
+        <v>94.38000000000001</v>
       </c>
       <c r="G61">
         <v>26.2</v>
@@ -6289,28 +6289,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M61">
-        <v>21.8838906</v>
+        <v>22.254804</v>
       </c>
       <c r="N61">
-        <v>-16.62878855918367</v>
+        <v>-16.99970195918367</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-16.62878855918367</v>
+        <v>-16.99970195918367</v>
       </c>
       <c r="Q61">
-        <v>30.87121144081633</v>
+        <v>30.50029804081633</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2269638594204815</v>
+        <v>0.2314929559059935</v>
       </c>
       <c r="T61">
-        <v>1.551810438914514</v>
+        <v>1.590605699887377</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2401356384415636</v>
+        <v>0.2361333778008708</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2340771823623974</v>
+        <v>0.2359771823623974</v>
       </c>
       <c r="C62">
-        <v>-3.005677051897663</v>
+        <v>-5.222166324501941</v>
       </c>
       <c r="D62">
-        <v>65.17432294810234</v>
+        <v>64.53083367549806</v>
       </c>
       <c r="E62">
-        <v>47.08000000000001</v>
+        <v>48.65300000000001</v>
       </c>
       <c r="F62">
-        <v>94.38000000000001</v>
+        <v>95.953</v>
       </c>
       <c r="G62">
         <v>26.2</v>
@@ -6371,28 +6371,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M62">
-        <v>22.254804</v>
+        <v>22.6257174</v>
       </c>
       <c r="N62">
-        <v>-16.99970195918367</v>
+        <v>-17.37061535918367</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-16.99970195918367</v>
+        <v>-17.37061535918367</v>
       </c>
       <c r="Q62">
-        <v>30.50029804081633</v>
+        <v>30.12938464081633</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2314929559059935</v>
+        <v>0.2362543137497369</v>
       </c>
       <c r="T62">
-        <v>1.590605699887377</v>
+        <v>1.63139046142295</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2361333778008708</v>
+        <v>0.2322623388205287</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2359771823623974</v>
+        <v>0.2378771823623974</v>
       </c>
       <c r="C63">
-        <v>-5.222166324501941</v>
+        <v>-7.42607303229633</v>
       </c>
       <c r="D63">
-        <v>64.53083367549806</v>
+        <v>63.89992696770368</v>
       </c>
       <c r="E63">
-        <v>48.65300000000001</v>
+        <v>50.22600000000001</v>
       </c>
       <c r="F63">
-        <v>95.953</v>
+        <v>97.52600000000001</v>
       </c>
       <c r="G63">
         <v>26.2</v>
@@ -6453,28 +6453,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M63">
-        <v>22.6257174</v>
+        <v>22.9966308</v>
       </c>
       <c r="N63">
-        <v>-17.37061535918367</v>
+        <v>-17.74152875918367</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-17.37061535918367</v>
+        <v>-17.74152875918367</v>
       </c>
       <c r="Q63">
-        <v>30.12938464081633</v>
+        <v>29.75847124081633</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2362543137497369</v>
+        <v>0.2412662693747301</v>
       </c>
       <c r="T63">
-        <v>1.63139046142295</v>
+        <v>1.674321789355133</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2322623388205287</v>
+        <v>0.2285161720653589</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2378771823623974</v>
+        <v>0.2397771823623974</v>
       </c>
       <c r="C64">
-        <v>-7.42607303229633</v>
+        <v>-9.617762654678373</v>
       </c>
       <c r="D64">
-        <v>63.89992696770368</v>
+        <v>63.28123734532164</v>
       </c>
       <c r="E64">
-        <v>50.22600000000001</v>
+        <v>51.79900000000001</v>
       </c>
       <c r="F64">
-        <v>97.52600000000001</v>
+        <v>99.099</v>
       </c>
       <c r="G64">
         <v>26.2</v>
@@ -6535,28 +6535,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M64">
-        <v>22.9966308</v>
+        <v>23.3675442</v>
       </c>
       <c r="N64">
-        <v>-17.74152875918367</v>
+        <v>-18.11244215918367</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-17.74152875918367</v>
+        <v>-18.11244215918367</v>
       </c>
       <c r="Q64">
-        <v>29.75847124081633</v>
+        <v>29.38755784081633</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2412662693747301</v>
+        <v>0.246549141519993</v>
       </c>
       <c r="T64">
-        <v>1.674321789355133</v>
+        <v>1.719573729607975</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2285161720653589</v>
+        <v>0.2248889312389246</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2397771823623974</v>
+        <v>0.2416771823623974</v>
       </c>
       <c r="C65">
-        <v>-9.617762654678373</v>
+        <v>-11.7975866522509</v>
       </c>
       <c r="D65">
-        <v>63.28123734532164</v>
+        <v>62.67441334774911</v>
       </c>
       <c r="E65">
-        <v>51.79900000000001</v>
+        <v>53.37200000000001</v>
       </c>
       <c r="F65">
-        <v>99.099</v>
+        <v>100.672</v>
       </c>
       <c r="G65">
         <v>26.2</v>
@@ -6617,28 +6617,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M65">
-        <v>23.3675442</v>
+        <v>23.7384576</v>
       </c>
       <c r="N65">
-        <v>-18.11244215918367</v>
+        <v>-18.48335555918367</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-18.11244215918367</v>
+        <v>-18.48335555918367</v>
       </c>
       <c r="Q65">
-        <v>29.38755784081633</v>
+        <v>29.01664444081633</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.246549141519993</v>
+        <v>0.252125506562215</v>
       </c>
       <c r="T65">
-        <v>1.719573729607975</v>
+        <v>1.76733966654153</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2248889312389246</v>
+        <v>0.2213750416883165</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2416771823623974</v>
+        <v>0.2435771823623974</v>
       </c>
       <c r="C66">
-        <v>-11.7975866522509</v>
+        <v>-13.96588313259127</v>
       </c>
       <c r="D66">
-        <v>62.67441334774911</v>
+        <v>62.07911686740873</v>
       </c>
       <c r="E66">
-        <v>53.37200000000001</v>
+        <v>54.94500000000001</v>
       </c>
       <c r="F66">
-        <v>100.672</v>
+        <v>102.245</v>
       </c>
       <c r="G66">
         <v>26.2</v>
@@ -6699,28 +6699,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M66">
-        <v>23.7384576</v>
+        <v>24.109371</v>
       </c>
       <c r="N66">
-        <v>-18.48335555918367</v>
+        <v>-18.85426895918367</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-18.48335555918367</v>
+        <v>-18.85426895918367</v>
       </c>
       <c r="Q66">
-        <v>29.01664444081633</v>
+        <v>28.64573104081633</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.252125506562215</v>
+        <v>0.2580205210354212</v>
       </c>
       <c r="T66">
-        <v>1.76733966654153</v>
+        <v>1.817835085585574</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2213750416883165</v>
+        <v>0.2179692718161885</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2435771823623974</v>
+        <v>0.2454771823623974</v>
       </c>
       <c r="C67">
-        <v>-13.96588313259127</v>
+        <v>-16.12297747843573</v>
       </c>
       <c r="D67">
-        <v>62.07911686740873</v>
+        <v>61.49502252156429</v>
       </c>
       <c r="E67">
-        <v>54.94500000000001</v>
+        <v>56.51800000000001</v>
       </c>
       <c r="F67">
-        <v>102.245</v>
+        <v>103.818</v>
       </c>
       <c r="G67">
         <v>26.2</v>
@@ -6781,28 +6781,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M67">
-        <v>24.109371</v>
+        <v>24.4802844</v>
       </c>
       <c r="N67">
-        <v>-18.85426895918367</v>
+        <v>-19.22518235918367</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-18.85426895918367</v>
+        <v>-19.22518235918367</v>
       </c>
       <c r="Q67">
-        <v>28.64573104081633</v>
+        <v>28.27481764081633</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2580205210354212</v>
+        <v>0.2642623010658747</v>
       </c>
       <c r="T67">
-        <v>1.817835085585574</v>
+        <v>1.871300823396914</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2179692718161885</v>
+        <v>0.2146667070917008</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2454771823623974</v>
+        <v>0.2473771823623974</v>
       </c>
       <c r="C68">
-        <v>-16.12297747843573</v>
+        <v>-18.2691829407314</v>
       </c>
       <c r="D68">
-        <v>61.49502252156429</v>
+        <v>60.92181705926862</v>
       </c>
       <c r="E68">
-        <v>56.51800000000001</v>
+        <v>58.09100000000002</v>
       </c>
       <c r="F68">
-        <v>103.818</v>
+        <v>105.391</v>
       </c>
       <c r="G68">
         <v>26.2</v>
@@ -6863,28 +6863,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M68">
-        <v>24.4802844</v>
+        <v>24.8511978</v>
       </c>
       <c r="N68">
-        <v>-19.22518235918367</v>
+        <v>-19.59609575918367</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-19.22518235918367</v>
+        <v>-19.59609575918367</v>
       </c>
       <c r="Q68">
-        <v>28.27481764081633</v>
+        <v>27.90390424081633</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2642623010658747</v>
+        <v>0.2708823707951437</v>
       </c>
       <c r="T68">
-        <v>1.871300823396914</v>
+        <v>1.928006908954396</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2146667070917008</v>
+        <v>0.2114627263888396</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2473771823623974</v>
+        <v>0.2492771823623974</v>
       </c>
       <c r="C69">
-        <v>-18.2691829407314</v>
+        <v>-20.40480119882683</v>
       </c>
       <c r="D69">
-        <v>60.92181705926862</v>
+        <v>60.35919880117318</v>
       </c>
       <c r="E69">
-        <v>58.09100000000002</v>
+        <v>59.66400000000002</v>
       </c>
       <c r="F69">
-        <v>105.391</v>
+        <v>106.964</v>
       </c>
       <c r="G69">
         <v>26.2</v>
@@ -6945,28 +6945,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M69">
-        <v>24.8511978</v>
+        <v>25.2221112</v>
       </c>
       <c r="N69">
-        <v>-19.59609575918367</v>
+        <v>-19.96700915918367</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-19.59609575918367</v>
+        <v>-19.96700915918367</v>
       </c>
       <c r="Q69">
-        <v>27.90390424081633</v>
+        <v>27.53299084081633</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2708823707951437</v>
+        <v>0.2779161948824919</v>
       </c>
       <c r="T69">
-        <v>1.928006908954396</v>
+        <v>1.988257124859221</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2114627263888396</v>
+        <v>0.2083529804125331</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2492771823623974</v>
+        <v>0.2511771823623974</v>
       </c>
       <c r="C70">
-        <v>-20.40480119882683</v>
+        <v>-22.53012288990629</v>
       </c>
       <c r="D70">
-        <v>60.35919880117318</v>
+        <v>59.80687711009373</v>
       </c>
       <c r="E70">
-        <v>59.66400000000002</v>
+        <v>61.23700000000002</v>
       </c>
       <c r="F70">
-        <v>106.964</v>
+        <v>108.537</v>
       </c>
       <c r="G70">
         <v>26.2</v>
@@ -7027,28 +7027,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M70">
-        <v>25.2221112</v>
+        <v>25.59302460000001</v>
       </c>
       <c r="N70">
-        <v>-19.96700915918367</v>
+        <v>-20.33792255918367</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-19.96700915918367</v>
+        <v>-20.33792255918367</v>
       </c>
       <c r="Q70">
-        <v>27.53299084081633</v>
+        <v>27.16207744081633</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2779161948824919</v>
+        <v>0.2854038140722498</v>
       </c>
       <c r="T70">
-        <v>1.988257124859221</v>
+        <v>2.052394451467583</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2083529804125331</v>
+        <v>0.2053333720007572</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2511771823623974</v>
+        <v>0.2530771823623974</v>
       </c>
       <c r="C71">
-        <v>-22.53012288990629</v>
+        <v>-24.64542810961969</v>
       </c>
       <c r="D71">
-        <v>59.80687711009373</v>
+        <v>59.26457189038033</v>
       </c>
       <c r="E71">
-        <v>61.23700000000002</v>
+        <v>62.81000000000002</v>
       </c>
       <c r="F71">
-        <v>108.537</v>
+        <v>110.11</v>
       </c>
       <c r="G71">
         <v>26.2</v>
@@ -7109,28 +7109,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M71">
-        <v>25.59302460000001</v>
+        <v>25.96393800000001</v>
       </c>
       <c r="N71">
-        <v>-20.33792255918367</v>
+        <v>-20.70883595918367</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-20.33792255918367</v>
+        <v>-20.70883595918367</v>
       </c>
       <c r="Q71">
-        <v>27.16207744081633</v>
+        <v>26.79116404081633</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2854038140722498</v>
+        <v>0.293390607874658</v>
       </c>
       <c r="T71">
-        <v>2.052394451467583</v>
+        <v>2.120807599849836</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2053333720007572</v>
+        <v>0.2024000381150322</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2530771823623974</v>
+        <v>0.2549771823623974</v>
       </c>
       <c r="C72">
-        <v>-24.64542810961969</v>
+        <v>-26.75098688572028</v>
       </c>
       <c r="D72">
-        <v>59.26457189038033</v>
+        <v>58.73201311427974</v>
       </c>
       <c r="E72">
-        <v>62.81000000000002</v>
+        <v>64.38300000000002</v>
       </c>
       <c r="F72">
-        <v>110.11</v>
+        <v>111.683</v>
       </c>
       <c r="G72">
         <v>26.2</v>
@@ -7191,28 +7191,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M72">
-        <v>25.96393800000001</v>
+        <v>26.33485140000001</v>
       </c>
       <c r="N72">
-        <v>-20.70883595918367</v>
+        <v>-21.07974935918367</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-20.70883595918367</v>
+        <v>-21.07974935918367</v>
       </c>
       <c r="Q72">
-        <v>26.79116404081633</v>
+        <v>26.42025064081633</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.293390607874658</v>
+        <v>0.3019282150427497</v>
       </c>
       <c r="T72">
-        <v>2.120807599849836</v>
+        <v>2.193938896396382</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2024000381150322</v>
+        <v>0.1995493333528486</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2549771823623974</v>
+        <v>0.2568771823623974</v>
       </c>
       <c r="C73">
-        <v>-26.75098688572027</v>
+        <v>-28.84705962639271</v>
       </c>
       <c r="D73">
-        <v>58.73201311427974</v>
+        <v>58.20894037360729</v>
       </c>
       <c r="E73">
-        <v>64.38300000000001</v>
+        <v>65.956</v>
       </c>
       <c r="F73">
-        <v>111.683</v>
+        <v>113.256</v>
       </c>
       <c r="G73">
         <v>26.2</v>
@@ -7273,28 +7273,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M73">
-        <v>26.3348514</v>
+        <v>26.7057648</v>
       </c>
       <c r="N73">
-        <v>-21.07974935918367</v>
+        <v>-21.45066275918367</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-21.07974935918367</v>
+        <v>-21.45066275918367</v>
       </c>
       <c r="Q73">
-        <v>26.42025064081633</v>
+        <v>26.04933724081633</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3019282150427497</v>
+        <v>0.3110756512942764</v>
       </c>
       <c r="T73">
-        <v>2.193938896396381</v>
+        <v>2.272293856981967</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1995493333528486</v>
+        <v>0.1967778148340591</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2568771823623974</v>
+        <v>0.2587771823623974</v>
       </c>
       <c r="C74">
-        <v>-28.84705962639271</v>
+        <v>-30.93389754483557</v>
       </c>
       <c r="D74">
-        <v>58.20894037360729</v>
+        <v>57.69510245516443</v>
       </c>
       <c r="E74">
-        <v>65.956</v>
+        <v>67.52900000000001</v>
       </c>
       <c r="F74">
-        <v>113.256</v>
+        <v>114.829</v>
       </c>
       <c r="G74">
         <v>26.2</v>
@@ -7355,28 +7355,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M74">
-        <v>26.7057648</v>
+        <v>27.0766782</v>
       </c>
       <c r="N74">
-        <v>-21.45066275918367</v>
+        <v>-21.82157615918367</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-21.45066275918367</v>
+        <v>-21.82157615918367</v>
       </c>
       <c r="Q74">
-        <v>26.04933724081633</v>
+        <v>25.67842384081633</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3110756512942764</v>
+        <v>0.3209006754162866</v>
       </c>
       <c r="T74">
-        <v>2.272293856981967</v>
+        <v>2.356452888722039</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1967778148340591</v>
+        <v>0.1940822283294829</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2587771823623974</v>
+        <v>0.2606771823623974</v>
       </c>
       <c r="C75">
-        <v>-30.93389754483557</v>
+        <v>-33.01174306155259</v>
       </c>
       <c r="D75">
-        <v>57.69510245516443</v>
+        <v>57.19025693844741</v>
       </c>
       <c r="E75">
-        <v>67.52900000000001</v>
+        <v>69.102</v>
       </c>
       <c r="F75">
-        <v>114.829</v>
+        <v>116.402</v>
       </c>
       <c r="G75">
         <v>26.2</v>
@@ -7437,28 +7437,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M75">
-        <v>27.0766782</v>
+        <v>27.4475916</v>
       </c>
       <c r="N75">
-        <v>-21.82157615918367</v>
+        <v>-22.19248955918367</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-21.82157615918367</v>
+        <v>-22.19248955918367</v>
       </c>
       <c r="Q75">
-        <v>25.67842384081633</v>
+        <v>25.30751044081633</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3209006754162866</v>
+        <v>0.3314814706246054</v>
       </c>
       <c r="T75">
-        <v>2.356452888722039</v>
+        <v>2.447085692134425</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1940822283294829</v>
+        <v>0.1914594955142196</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2606771823623974</v>
+        <v>0.2625771823623974</v>
       </c>
       <c r="C76">
-        <v>-33.01174306155259</v>
+        <v>-35.08083018570636</v>
       </c>
       <c r="D76">
-        <v>57.19025693844741</v>
+        <v>56.69416981429364</v>
       </c>
       <c r="E76">
-        <v>69.102</v>
+        <v>70.67500000000001</v>
       </c>
       <c r="F76">
-        <v>116.402</v>
+        <v>117.975</v>
       </c>
       <c r="G76">
         <v>26.2</v>
@@ -7519,28 +7519,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M76">
-        <v>27.4475916</v>
+        <v>27.818505</v>
       </c>
       <c r="N76">
-        <v>-22.19248955918367</v>
+        <v>-22.56340295918367</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-22.19248955918367</v>
+        <v>-22.56340295918367</v>
       </c>
       <c r="Q76">
-        <v>25.30751044081633</v>
+        <v>24.93659704081633</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3314814706246054</v>
+        <v>0.3429087294495897</v>
       </c>
       <c r="T76">
-        <v>2.447085692134425</v>
+        <v>2.544969119819803</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1914594955142196</v>
+        <v>0.1889067022406967</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2625771823623974</v>
+        <v>0.2644771823623974</v>
       </c>
       <c r="C77">
-        <v>-35.08083018570636</v>
+        <v>-37.14138487679475</v>
       </c>
       <c r="D77">
-        <v>56.69416981429364</v>
+        <v>56.20661512320527</v>
       </c>
       <c r="E77">
-        <v>70.67500000000001</v>
+        <v>72.24800000000002</v>
       </c>
       <c r="F77">
-        <v>117.975</v>
+        <v>119.548</v>
       </c>
       <c r="G77">
         <v>26.2</v>
@@ -7601,28 +7601,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M77">
-        <v>27.818505</v>
+        <v>28.1894184</v>
       </c>
       <c r="N77">
-        <v>-22.56340295918367</v>
+        <v>-22.93431635918367</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-22.56340295918367</v>
+        <v>-22.93431635918367</v>
       </c>
       <c r="Q77">
-        <v>24.93659704081633</v>
+        <v>24.56568364081633</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3429087294495897</v>
+        <v>0.3552882598433226</v>
       </c>
       <c r="T77">
-        <v>2.544969119819803</v>
+        <v>2.651009499812294</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1889067022406967</v>
+        <v>0.1864210877375296</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2644771823623974</v>
+        <v>0.2663771823623974</v>
       </c>
       <c r="C78">
-        <v>-37.14138487679475</v>
+        <v>-39.19362538782438</v>
       </c>
       <c r="D78">
-        <v>56.20661512320527</v>
+        <v>55.72737461217562</v>
       </c>
       <c r="E78">
-        <v>72.24800000000002</v>
+        <v>73.82100000000001</v>
       </c>
       <c r="F78">
-        <v>119.548</v>
+        <v>121.121</v>
       </c>
       <c r="G78">
         <v>26.2</v>
@@ -7683,28 +7683,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M78">
-        <v>28.1894184</v>
+        <v>28.5603318</v>
       </c>
       <c r="N78">
-        <v>-22.93431635918367</v>
+        <v>-23.30522975918367</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-22.93431635918367</v>
+        <v>-23.30522975918367</v>
       </c>
       <c r="Q78">
-        <v>24.56568364081633</v>
+        <v>24.19477024081633</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3552882598433226</v>
+        <v>0.3687442711408583</v>
       </c>
       <c r="T78">
-        <v>2.651009499812294</v>
+        <v>2.766270782412829</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1864210877375296</v>
+        <v>0.1840000346500292</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2663771823623974</v>
+        <v>0.2682771823623974</v>
       </c>
       <c r="C79">
-        <v>-39.19362538782438</v>
+        <v>-41.23776259107677</v>
       </c>
       <c r="D79">
-        <v>55.72737461217562</v>
+        <v>55.25623740892324</v>
       </c>
       <c r="E79">
-        <v>73.82100000000001</v>
+        <v>75.39400000000002</v>
       </c>
       <c r="F79">
-        <v>121.121</v>
+        <v>122.694</v>
       </c>
       <c r="G79">
         <v>26.2</v>
@@ -7765,28 +7765,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M79">
-        <v>28.5603318</v>
+        <v>28.93124520000001</v>
       </c>
       <c r="N79">
-        <v>-23.30522975918367</v>
+        <v>-23.67614315918367</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-23.30522975918367</v>
+        <v>-23.67614315918367</v>
       </c>
       <c r="Q79">
-        <v>24.19477024081633</v>
+        <v>23.82385684081633</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3687442711408583</v>
+        <v>0.3834235561927155</v>
       </c>
       <c r="T79">
-        <v>2.766270782412829</v>
+        <v>2.892010363431594</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1840000346500292</v>
+        <v>0.1816410598468237</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2682771823623974</v>
+        <v>0.2701771823623974</v>
       </c>
       <c r="C80">
-        <v>-41.23776259107677</v>
+        <v>-43.27400028748747</v>
       </c>
       <c r="D80">
-        <v>55.25623740892324</v>
+        <v>54.79299971251255</v>
       </c>
       <c r="E80">
-        <v>75.39400000000002</v>
+        <v>76.96700000000001</v>
       </c>
       <c r="F80">
-        <v>122.694</v>
+        <v>124.267</v>
       </c>
       <c r="G80">
         <v>26.2</v>
@@ -7847,28 +7847,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M80">
-        <v>28.93124520000001</v>
+        <v>29.3021586</v>
       </c>
       <c r="N80">
-        <v>-23.67614315918367</v>
+        <v>-24.04705655918367</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-23.67614315918367</v>
+        <v>-24.04705655918367</v>
       </c>
       <c r="Q80">
-        <v>23.82385684081633</v>
+        <v>23.45294344081633</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3834235561927155</v>
+        <v>0.3995008683923687</v>
       </c>
       <c r="T80">
-        <v>2.892010363431594</v>
+        <v>3.029725142642623</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1816410598468237</v>
+        <v>0.179341805924712</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2701771823623974</v>
+        <v>0.2720771823623974</v>
       </c>
       <c r="C81">
-        <v>-43.27400028748747</v>
+        <v>-45.30253550059336</v>
       </c>
       <c r="D81">
-        <v>54.79299971251255</v>
+        <v>54.33746449940665</v>
       </c>
       <c r="E81">
-        <v>76.96700000000001</v>
+        <v>78.54000000000002</v>
       </c>
       <c r="F81">
-        <v>124.267</v>
+        <v>125.84</v>
       </c>
       <c r="G81">
         <v>26.2</v>
@@ -7929,28 +7929,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M81">
-        <v>29.3021586</v>
+        <v>29.673072</v>
       </c>
       <c r="N81">
-        <v>-24.04705655918367</v>
+        <v>-24.41796995918367</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-24.04705655918367</v>
+        <v>-24.41796995918367</v>
       </c>
       <c r="Q81">
-        <v>23.45294344081633</v>
+        <v>23.08203004081633</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3995008683923687</v>
+        <v>0.4171859118119872</v>
       </c>
       <c r="T81">
-        <v>3.029725142642623</v>
+        <v>3.181211399774754</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.179341805924712</v>
+        <v>0.1771000333506532</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2720771823623974</v>
+        <v>0.2739771823623974</v>
       </c>
       <c r="C82">
-        <v>-45.30253550059336</v>
+        <v>-47.32355875593754</v>
       </c>
       <c r="D82">
-        <v>54.33746449940665</v>
+        <v>53.88944124406247</v>
       </c>
       <c r="E82">
-        <v>78.54000000000002</v>
+        <v>80.11300000000001</v>
       </c>
       <c r="F82">
-        <v>125.84</v>
+        <v>127.413</v>
       </c>
       <c r="G82">
         <v>26.2</v>
@@ -8011,28 +8011,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M82">
-        <v>29.673072</v>
+        <v>30.0439854</v>
       </c>
       <c r="N82">
-        <v>-24.41796995918367</v>
+        <v>-24.78888335918367</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-24.41796995918367</v>
+        <v>-24.78888335918367</v>
       </c>
       <c r="Q82">
-        <v>23.08203004081633</v>
+        <v>22.71111664081633</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4171859118119872</v>
+        <v>0.4367325387494602</v>
       </c>
       <c r="T82">
-        <v>3.181211399774754</v>
+        <v>3.348643578710267</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1771000333506532</v>
+        <v>0.1749136131858302</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2739771823623974</v>
+        <v>0.2758771823623974</v>
       </c>
       <c r="C83">
-        <v>-47.32355875593754</v>
+        <v>-49.33725434676487</v>
       </c>
       <c r="D83">
-        <v>53.88944124406247</v>
+        <v>53.44874565323516</v>
       </c>
       <c r="E83">
-        <v>80.11300000000001</v>
+        <v>81.68600000000002</v>
       </c>
       <c r="F83">
-        <v>127.413</v>
+        <v>128.986</v>
       </c>
       <c r="G83">
         <v>26.2</v>
@@ -8093,28 +8093,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M83">
-        <v>30.0439854</v>
+        <v>30.41489880000001</v>
       </c>
       <c r="N83">
-        <v>-24.78888335918367</v>
+        <v>-25.15979675918367</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-24.78888335918367</v>
+        <v>-25.15979675918367</v>
       </c>
       <c r="Q83">
-        <v>22.71111664081633</v>
+        <v>22.34020324081633</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4367325387494602</v>
+        <v>0.4584510131244302</v>
       </c>
       <c r="T83">
-        <v>3.348643578710267</v>
+        <v>3.53467933308306</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1749136131858302</v>
+        <v>0.1727805203421006</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2758771823623974</v>
+        <v>0.2777771823623975</v>
       </c>
       <c r="C84">
-        <v>-49.33725434676487</v>
+        <v>-51.34380058678659</v>
       </c>
       <c r="D84">
-        <v>53.44874565323516</v>
+        <v>53.01519941321344</v>
       </c>
       <c r="E84">
-        <v>81.68600000000002</v>
+        <v>83.25900000000003</v>
       </c>
       <c r="F84">
-        <v>128.986</v>
+        <v>130.559</v>
       </c>
       <c r="G84">
         <v>26.2</v>
@@ -8175,28 +8175,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M84">
-        <v>30.41489880000001</v>
+        <v>30.78581220000001</v>
       </c>
       <c r="N84">
-        <v>-25.15979675918367</v>
+        <v>-25.53071015918367</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-25.15979675918367</v>
+        <v>-25.53071015918367</v>
       </c>
       <c r="Q84">
-        <v>22.34020324081633</v>
+        <v>21.96928984081633</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4584510131244302</v>
+        <v>0.4827246021317497</v>
       </c>
       <c r="T84">
-        <v>3.53467933308306</v>
+        <v>3.742601646793829</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1727805203421006</v>
+        <v>0.1706988273259308</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2777771823623975</v>
+        <v>0.2796771823623974</v>
       </c>
       <c r="C85">
-        <v>-51.34380058678659</v>
+        <v>-53.34337005074207</v>
       </c>
       <c r="D85">
-        <v>53.01519941321344</v>
+        <v>52.58862994925796</v>
       </c>
       <c r="E85">
-        <v>83.25900000000003</v>
+        <v>84.83200000000004</v>
       </c>
       <c r="F85">
-        <v>130.559</v>
+        <v>132.132</v>
       </c>
       <c r="G85">
         <v>26.2</v>
@@ -8257,28 +8257,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M85">
-        <v>30.78581220000001</v>
+        <v>31.15672560000001</v>
       </c>
       <c r="N85">
-        <v>-25.53071015918367</v>
+        <v>-25.90162355918368</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-25.53071015918367</v>
+        <v>-25.90162355918368</v>
       </c>
       <c r="Q85">
-        <v>21.96928984081633</v>
+        <v>21.59837644081632</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4827246021317497</v>
+        <v>0.510032389764984</v>
       </c>
       <c r="T85">
-        <v>3.742601646793829</v>
+        <v>3.976514249718444</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1706988273259308</v>
+        <v>0.1686666984291935</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2796771823623974</v>
+        <v>0.2815771823623974</v>
       </c>
       <c r="C86">
-        <v>-53.34337005074204</v>
+        <v>-55.33612980343977</v>
       </c>
       <c r="D86">
-        <v>52.58862994925796</v>
+        <v>52.16887019656024</v>
       </c>
       <c r="E86">
-        <v>84.83200000000001</v>
+        <v>86.40500000000002</v>
       </c>
       <c r="F86">
-        <v>132.132</v>
+        <v>133.705</v>
       </c>
       <c r="G86">
         <v>26.2</v>
@@ -8339,28 +8339,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M86">
-        <v>31.1567256</v>
+        <v>31.527639</v>
       </c>
       <c r="N86">
-        <v>-25.90162355918367</v>
+        <v>-26.27253695918367</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-25.90162355918367</v>
+        <v>-26.27253695918367</v>
       </c>
       <c r="Q86">
-        <v>21.59837644081633</v>
+        <v>21.22746304081633</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5100323897649837</v>
+        <v>0.540981215749316</v>
       </c>
       <c r="T86">
-        <v>3.976514249718441</v>
+        <v>4.24161519969967</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1686666984291935</v>
+        <v>0.1666823843300265</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2815771823623974</v>
+        <v>0.2834771823623974</v>
       </c>
       <c r="C87">
-        <v>-55.33612980343977</v>
+        <v>-57.32224161791579</v>
       </c>
       <c r="D87">
-        <v>52.16887019656024</v>
+        <v>51.75575838208422</v>
       </c>
       <c r="E87">
-        <v>86.40500000000002</v>
+        <v>87.97800000000002</v>
       </c>
       <c r="F87">
-        <v>133.705</v>
+        <v>135.278</v>
       </c>
       <c r="G87">
         <v>26.2</v>
@@ -8421,28 +8421,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M87">
-        <v>31.527639</v>
+        <v>31.89855240000001</v>
       </c>
       <c r="N87">
-        <v>-26.27253695918367</v>
+        <v>-26.64345035918367</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-26.27253695918367</v>
+        <v>-26.64345035918367</v>
       </c>
       <c r="Q87">
-        <v>21.22746304081633</v>
+        <v>20.85654964081633</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.540981215749316</v>
+        <v>0.5763513025885528</v>
       </c>
       <c r="T87">
-        <v>4.24161519969967</v>
+        <v>4.544587713963933</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1666823843300265</v>
+        <v>0.164744217070375</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2834771823623974</v>
+        <v>0.2853771823623974</v>
       </c>
       <c r="C88">
-        <v>-57.32224161791579</v>
+        <v>-59.30186218330866</v>
       </c>
       <c r="D88">
-        <v>51.75575838208422</v>
+        <v>51.34913781669135</v>
       </c>
       <c r="E88">
-        <v>87.97800000000002</v>
+        <v>89.551</v>
       </c>
       <c r="F88">
-        <v>135.278</v>
+        <v>136.851</v>
       </c>
       <c r="G88">
         <v>26.2</v>
@@ -8503,28 +8503,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M88">
-        <v>31.89855240000001</v>
+        <v>32.2694658</v>
       </c>
       <c r="N88">
-        <v>-26.64345035918367</v>
+        <v>-27.01436375918367</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-26.64345035918367</v>
+        <v>-27.01436375918367</v>
       </c>
       <c r="Q88">
-        <v>20.85654964081633</v>
+        <v>20.48563624081633</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5763513025885528</v>
+        <v>0.6171629412492107</v>
       </c>
       <c r="T88">
-        <v>4.544587713963933</v>
+        <v>4.894171384268851</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.164744217070375</v>
+        <v>0.1628506053799109</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2853771823623974</v>
+        <v>0.2872771823623974</v>
       </c>
       <c r="C89">
-        <v>-59.30186218330866</v>
+        <v>-61.27514330301149</v>
       </c>
       <c r="D89">
-        <v>51.34913781669135</v>
+        <v>50.94885669698851</v>
       </c>
       <c r="E89">
-        <v>89.551</v>
+        <v>91.12400000000001</v>
       </c>
       <c r="F89">
-        <v>136.851</v>
+        <v>138.424</v>
       </c>
       <c r="G89">
         <v>26.2</v>
@@ -8585,28 +8585,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M89">
-        <v>32.2694658</v>
+        <v>32.64037920000001</v>
       </c>
       <c r="N89">
-        <v>-27.01436375918367</v>
+        <v>-27.38527715918367</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-27.01436375918367</v>
+        <v>-27.38527715918367</v>
       </c>
       <c r="Q89">
-        <v>20.48563624081633</v>
+        <v>20.11472284081633</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6171629412492107</v>
+        <v>0.6647765196866451</v>
       </c>
       <c r="T89">
-        <v>4.894171384268851</v>
+        <v>5.302018999624589</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1628506053799109</v>
+        <v>0.1610000303187755</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2872771823623974</v>
+        <v>0.2891771823623974</v>
       </c>
       <c r="C90">
-        <v>-61.27514330301149</v>
+        <v>-63.2422320836279</v>
       </c>
       <c r="D90">
-        <v>50.94885669698851</v>
+        <v>50.55476791637212</v>
       </c>
       <c r="E90">
-        <v>91.12400000000001</v>
+        <v>92.69700000000002</v>
       </c>
       <c r="F90">
-        <v>138.424</v>
+        <v>139.997</v>
       </c>
       <c r="G90">
         <v>26.2</v>
@@ -8667,28 +8667,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M90">
-        <v>32.64037920000001</v>
+        <v>33.0112926</v>
       </c>
       <c r="N90">
-        <v>-27.38527715918367</v>
+        <v>-27.75619055918367</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-27.38527715918367</v>
+        <v>-27.75619055918367</v>
       </c>
       <c r="Q90">
-        <v>20.11472284081633</v>
+        <v>19.74380944081633</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6647765196866451</v>
+        <v>0.721047112385431</v>
       </c>
       <c r="T90">
-        <v>5.302018999624589</v>
+        <v>5.784020726863188</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1610000303187755</v>
+        <v>0.1591910412140702</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2891771823623974</v>
+        <v>0.2910771823623974</v>
       </c>
       <c r="C91">
-        <v>-63.2422320836279</v>
+        <v>-65.20327111522566</v>
       </c>
       <c r="D91">
-        <v>50.55476791637212</v>
+        <v>50.16672888477436</v>
       </c>
       <c r="E91">
-        <v>92.69700000000002</v>
+        <v>94.27000000000002</v>
       </c>
       <c r="F91">
-        <v>139.997</v>
+        <v>141.57</v>
       </c>
       <c r="G91">
         <v>26.2</v>
@@ -8749,28 +8749,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M91">
-        <v>33.0112926</v>
+        <v>33.382206</v>
       </c>
       <c r="N91">
-        <v>-27.75619055918367</v>
+        <v>-28.12710395918367</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-27.75619055918367</v>
+        <v>-28.12710395918367</v>
       </c>
       <c r="Q91">
-        <v>19.74380944081633</v>
+        <v>19.37289604081633</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.721047112385431</v>
+        <v>0.7885718236239743</v>
       </c>
       <c r="T91">
-        <v>5.784020726863188</v>
+        <v>6.362422799549508</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1591910412140702</v>
+        <v>0.1574222518672472</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2910771823623974</v>
+        <v>0.2929771823623974</v>
       </c>
       <c r="C92">
-        <v>-65.20327111522566</v>
+        <v>-67.15839864335263</v>
       </c>
       <c r="D92">
-        <v>50.16672888477436</v>
+        <v>49.78460135664741</v>
       </c>
       <c r="E92">
-        <v>94.27000000000002</v>
+        <v>95.84300000000003</v>
       </c>
       <c r="F92">
-        <v>141.57</v>
+        <v>143.143</v>
       </c>
       <c r="G92">
         <v>26.2</v>
@@ -8831,28 +8831,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M92">
-        <v>33.382206</v>
+        <v>33.75311940000001</v>
       </c>
       <c r="N92">
-        <v>-28.12710395918367</v>
+        <v>-28.49801735918368</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-28.12710395918367</v>
+        <v>-28.49801735918368</v>
       </c>
       <c r="Q92">
-        <v>19.37289604081633</v>
+        <v>19.00198264081632</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7885718236239743</v>
+        <v>0.8711020262488602</v>
       </c>
       <c r="T92">
-        <v>6.362422799549508</v>
+        <v>7.06935866616612</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1574222518672472</v>
+        <v>0.1556923370115632</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2929771823623974</v>
+        <v>0.2948771823623974</v>
       </c>
       <c r="C93">
-        <v>-67.15839864335263</v>
+        <v>-69.10774873324991</v>
       </c>
       <c r="D93">
-        <v>49.78460135664741</v>
+        <v>49.4082512667501</v>
       </c>
       <c r="E93">
-        <v>95.84300000000003</v>
+        <v>97.41600000000001</v>
       </c>
       <c r="F93">
-        <v>143.143</v>
+        <v>144.716</v>
       </c>
       <c r="G93">
         <v>26.2</v>
@@ -8913,28 +8913,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M93">
-        <v>33.75311940000001</v>
+        <v>34.1240328</v>
       </c>
       <c r="N93">
-        <v>-28.49801735918368</v>
+        <v>-28.86893075918367</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-28.49801735918368</v>
+        <v>-28.86893075918367</v>
       </c>
       <c r="Q93">
-        <v>19.00198264081632</v>
+        <v>18.63106924081633</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8711020262488602</v>
+        <v>0.974264779529968</v>
       </c>
       <c r="T93">
-        <v>7.06935866616612</v>
+        <v>7.953028499436887</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1556923370115632</v>
+        <v>0.154000029000568</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2948771823623974</v>
+        <v>0.2967771823623974</v>
       </c>
       <c r="C94">
-        <v>-69.10774873324991</v>
+        <v>-71.05145142667321</v>
       </c>
       <c r="D94">
-        <v>49.4082512667501</v>
+        <v>49.0375485733268</v>
       </c>
       <c r="E94">
-        <v>97.41600000000001</v>
+        <v>98.98900000000002</v>
       </c>
       <c r="F94">
-        <v>144.716</v>
+        <v>146.289</v>
       </c>
       <c r="G94">
         <v>26.2</v>
@@ -8995,28 +8995,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M94">
-        <v>34.1240328</v>
+        <v>34.49494620000001</v>
       </c>
       <c r="N94">
-        <v>-28.86893075918367</v>
+        <v>-29.23984415918368</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-28.86893075918367</v>
+        <v>-29.23984415918368</v>
       </c>
       <c r="Q94">
-        <v>18.63106924081633</v>
+        <v>18.26015584081632</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.974264779529968</v>
+        <v>1.106902605177106</v>
       </c>
       <c r="T94">
-        <v>7.953028499436887</v>
+        <v>9.089175427927872</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.154000029000568</v>
+        <v>0.1523441147102392</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2967771823623974</v>
+        <v>0.2986771823623974</v>
       </c>
       <c r="C95">
-        <v>-71.05145142667321</v>
+        <v>-72.98963289170668</v>
       </c>
       <c r="D95">
-        <v>49.0375485733268</v>
+        <v>48.67236710829335</v>
       </c>
       <c r="E95">
-        <v>98.98900000000002</v>
+        <v>100.562</v>
       </c>
       <c r="F95">
-        <v>146.289</v>
+        <v>147.862</v>
       </c>
       <c r="G95">
         <v>26.2</v>
@@ -9077,28 +9077,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M95">
-        <v>34.49494620000001</v>
+        <v>34.86585960000001</v>
       </c>
       <c r="N95">
-        <v>-29.23984415918368</v>
+        <v>-29.61075755918367</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-29.23984415918368</v>
+        <v>-29.61075755918367</v>
       </c>
       <c r="Q95">
-        <v>18.26015584081632</v>
+        <v>17.88924244081633</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.106902605177106</v>
+        <v>1.283753039373291</v>
       </c>
       <c r="T95">
-        <v>9.089175427927872</v>
+        <v>10.60403799924919</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1523441147102392</v>
+        <v>0.1507234326388537</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2986771823623974</v>
+        <v>0.3005771823623974</v>
       </c>
       <c r="C96">
-        <v>-72.98963289170668</v>
+        <v>-74.92241556593238</v>
       </c>
       <c r="D96">
-        <v>48.67236710829335</v>
+        <v>48.31258443406765</v>
       </c>
       <c r="E96">
-        <v>100.562</v>
+        <v>102.135</v>
       </c>
       <c r="F96">
-        <v>147.862</v>
+        <v>149.435</v>
       </c>
       <c r="G96">
         <v>26.2</v>
@@ -9159,28 +9159,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M96">
-        <v>34.86585960000001</v>
+        <v>35.23677300000001</v>
       </c>
       <c r="N96">
-        <v>-29.61075755918367</v>
+        <v>-29.98167095918367</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-29.61075755918367</v>
+        <v>-29.98167095918367</v>
       </c>
       <c r="Q96">
-        <v>17.88924244081633</v>
+        <v>17.51832904081633</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.283753039373291</v>
+        <v>1.53134364724795</v>
       </c>
       <c r="T96">
-        <v>10.60403799924919</v>
+        <v>12.72484559909903</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1507234326388537</v>
+        <v>0.1491368701900236</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3005771823623974</v>
+        <v>0.3024771823623974</v>
       </c>
       <c r="C97">
-        <v>-74.92241556593238</v>
+        <v>-76.8499182932968</v>
       </c>
       <c r="D97">
-        <v>48.31258443406765</v>
+        <v>47.95808170670321</v>
       </c>
       <c r="E97">
-        <v>102.135</v>
+        <v>103.708</v>
       </c>
       <c r="F97">
-        <v>149.435</v>
+        <v>151.008</v>
       </c>
       <c r="G97">
         <v>26.2</v>
@@ -9241,28 +9241,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M97">
-        <v>35.23677300000001</v>
+        <v>35.60768640000001</v>
       </c>
       <c r="N97">
-        <v>-29.98167095918367</v>
+        <v>-30.35258435918367</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-29.98167095918367</v>
+        <v>-30.35258435918367</v>
       </c>
       <c r="Q97">
-        <v>17.51832904081633</v>
+        <v>17.14741564081633</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.53134364724795</v>
+        <v>1.902729559059939</v>
       </c>
       <c r="T97">
-        <v>12.72484559909903</v>
+        <v>15.9060569988738</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1491368701900236</v>
+        <v>0.1475833611255443</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3024771823623974</v>
+        <v>0.3043771823623974</v>
       </c>
       <c r="C98">
-        <v>-76.8499182932968</v>
+        <v>-78.77225645499524</v>
       </c>
       <c r="D98">
-        <v>47.95808170670321</v>
+        <v>47.60874354500477</v>
       </c>
       <c r="E98">
-        <v>103.708</v>
+        <v>105.281</v>
       </c>
       <c r="F98">
-        <v>151.008</v>
+        <v>152.581</v>
       </c>
       <c r="G98">
         <v>26.2</v>
@@ -9323,28 +9323,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M98">
-        <v>35.60768640000001</v>
+        <v>35.9785998</v>
       </c>
       <c r="N98">
-        <v>-30.35258435918367</v>
+        <v>-30.72349775918367</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-30.35258435918367</v>
+        <v>-30.72349775918367</v>
       </c>
       <c r="Q98">
-        <v>17.14741564081633</v>
+        <v>16.77650224081633</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.902729559059934</v>
+        <v>2.521706078746578</v>
       </c>
       <c r="T98">
-        <v>15.90605699887375</v>
+        <v>21.20807599849834</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1475833611255443</v>
+        <v>0.1460618831757964</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3043771823623974</v>
+        <v>0.3062771823623974</v>
       </c>
       <c r="C99">
-        <v>-78.77225645499524</v>
+        <v>-80.68954209467734</v>
       </c>
       <c r="D99">
-        <v>47.60874354500477</v>
+        <v>47.26445790532266</v>
       </c>
       <c r="E99">
-        <v>105.281</v>
+        <v>106.854</v>
       </c>
       <c r="F99">
-        <v>152.581</v>
+        <v>154.154</v>
       </c>
       <c r="G99">
         <v>26.2</v>
@@ -9405,28 +9405,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M99">
-        <v>35.9785998</v>
+        <v>36.3495132</v>
       </c>
       <c r="N99">
-        <v>-30.72349775918367</v>
+        <v>-31.09441115918367</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-30.72349775918367</v>
+        <v>-31.09441115918367</v>
       </c>
       <c r="Q99">
-        <v>16.77650224081633</v>
+        <v>16.40558884081633</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.521706078746578</v>
+        <v>3.759659118119867</v>
       </c>
       <c r="T99">
-        <v>21.20807599849834</v>
+        <v>31.81211399774751</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1460618831757964</v>
+        <v>0.1445714557964516</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3062771823623974</v>
+        <v>0.3081771823623974</v>
       </c>
       <c r="C100">
-        <v>-80.68954209467734</v>
+        <v>-82.60188403825904</v>
       </c>
       <c r="D100">
-        <v>47.26445790532266</v>
+        <v>46.92511596174096</v>
       </c>
       <c r="E100">
-        <v>106.854</v>
+        <v>108.427</v>
       </c>
       <c r="F100">
-        <v>154.154</v>
+        <v>155.727</v>
       </c>
       <c r="G100">
         <v>26.2</v>
@@ -9487,28 +9487,28 @@
         <v>5.255102040816332</v>
       </c>
       <c r="M100">
-        <v>36.3495132</v>
+        <v>36.7204266</v>
       </c>
       <c r="N100">
-        <v>-31.09441115918367</v>
+        <v>-31.46532455918367</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-31.09441115918367</v>
+        <v>-31.46532455918367</v>
       </c>
       <c r="Q100">
-        <v>16.40558884081633</v>
+        <v>16.03467544081633</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.759659118119867</v>
+        <v>7.473518236239735</v>
       </c>
       <c r="T100">
-        <v>31.81211399774751</v>
+        <v>63.62422799549501</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1445714557964516</v>
+        <v>0.1431111380611338</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3081771823623974</v>
-      </c>
-      <c r="C101">
-        <v>-82.60188403825904</v>
-      </c>
-      <c r="D101">
-        <v>46.92511596174096</v>
-      </c>
-      <c r="E101">
-        <v>108.427</v>
-      </c>
-      <c r="F101">
-        <v>155.727</v>
-      </c>
-      <c r="G101">
-        <v>26.2</v>
-      </c>
-      <c r="H101">
-        <v>110</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>52.75510204081633</v>
-      </c>
-      <c r="K101">
-        <v>47.5</v>
-      </c>
-      <c r="L101">
-        <v>5.255102040816332</v>
-      </c>
-      <c r="M101">
-        <v>36.7204266</v>
-      </c>
-      <c r="N101">
-        <v>-31.46532455918367</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-31.46532455918367</v>
-      </c>
-      <c r="Q101">
-        <v>16.03467544081633</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.473518236239735</v>
-      </c>
-      <c r="T101">
-        <v>63.62422799549501</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1431111380611338</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
